--- a/AAII_Financials/Quarterly/LCID_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LCID_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -656,192 +656,199 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>157200</v>
+      </c>
+      <c r="E8" s="3">
         <v>137800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>150900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>149400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>257700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>195500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>97300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>57700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>26400</v>
-      </c>
-      <c r="L8" s="3">
-        <v>200</v>
       </c>
       <c r="M8" s="3">
         <v>200</v>
       </c>
       <c r="N8" s="3">
+        <v>200</v>
+      </c>
+      <c r="O8" s="3">
         <v>300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3600</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S8" s="3">
-        <v>0</v>
+      <c r="S8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>410000</v>
+      </c>
+      <c r="E9" s="3">
         <v>469700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>555800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>500500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>615300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>492500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>292300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>246000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>151500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3300</v>
       </c>
-      <c r="M9" s="3">
-        <v>0</v>
-      </c>
       <c r="N9" s="3">
+        <v>0</v>
+      </c>
+      <c r="O9" s="3">
         <v>100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2500</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
@@ -854,50 +861,53 @@
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-252800</v>
+      </c>
+      <c r="E10" s="3">
         <v>-331900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-404900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-351100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-357600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-297000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-195000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-188300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-125100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-3100</v>
-      </c>
-      <c r="M10" s="3">
-        <v>200</v>
       </c>
       <c r="N10" s="3">
         <v>200</v>
       </c>
       <c r="O10" s="3">
+        <v>200</v>
+      </c>
+      <c r="P10" s="3">
         <v>1100</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
@@ -910,8 +920,11 @@
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -932,50 +945,51 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>243000</v>
+      </c>
+      <c r="E12" s="3">
         <v>230800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>233500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>229800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>221300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>213800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>200400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>186100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>163600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>242400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>176800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>167400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>169500</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
@@ -988,8 +1002,11 @@
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1044,41 +1061,44 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>22500</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
         <v>0</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
+      <c r="I14" s="3">
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>2700</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1094,14 +1114,17 @@
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1156,8 +1179,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1175,55 +1201,56 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>894000</v>
+      </c>
+      <c r="E17" s="3">
         <v>890700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>988600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>921600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1007500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>883000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>656500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>655200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>512100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>500000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>249100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>299100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>203300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>300</v>
       </c>
-      <c r="Q17" s="3">
-        <v>0</v>
-      </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
+      <c r="R17" s="3">
+        <v>0</v>
       </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
@@ -1231,50 +1258,53 @@
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-736800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-752900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-837700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-772200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-749800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-687500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-559200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-597500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-485700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-499800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-248900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-298800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-199700</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1287,8 +1317,11 @@
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1309,50 +1342,51 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>90800</v>
+      </c>
+      <c r="E20" s="3">
         <v>123500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>75200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-6000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>278200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>158400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>339000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>516700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-559900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-24500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-12700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-449100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-111400</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1365,50 +1399,53 @@
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-578500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-568600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-707100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-728300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-416300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-478400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-177800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-42600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1009200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-509400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-254800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-743000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-306400</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1421,13 +1458,16 @@
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>1200</v>
+        <v>7800</v>
       </c>
       <c r="E22" s="3">
         <v>1200</v>
@@ -1436,13 +1476,13 @@
         <v>1200</v>
       </c>
       <c r="G22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H22" s="3">
         <v>1300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>900</v>
-      </c>
-      <c r="I22" s="3">
-        <v>100</v>
       </c>
       <c r="J22" s="3">
         <v>100</v>
@@ -1460,10 +1500,10 @@
         <v>100</v>
       </c>
       <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="P22" s="3">
+        <v>0</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>3</v>
@@ -1477,55 +1517,58 @@
       <c r="T22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-653800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-630600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-763600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-779400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-472800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-530000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-220400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-81000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1045700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-524400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-261700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-747900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-311200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-200</v>
       </c>
-      <c r="Q23" s="3">
-        <v>0</v>
-      </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
+      <c r="R23" s="3">
+        <v>0</v>
       </c>
       <c r="S23" s="3" t="s">
         <v>3</v>
@@ -1533,35 +1576,38 @@
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-200</v>
-      </c>
-      <c r="H24" s="3">
-        <v>100</v>
       </c>
       <c r="I24" s="3">
         <v>100</v>
       </c>
       <c r="J24" s="3">
+        <v>100</v>
+      </c>
+      <c r="K24" s="3">
         <v>300</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
         <v>0</v>
       </c>
@@ -1572,16 +1618,16 @@
         <v>0</v>
       </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>100</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>3</v>
+      <c r="R24" s="3">
+        <v>0</v>
       </c>
       <c r="S24" s="3" t="s">
         <v>3</v>
@@ -1589,8 +1635,11 @@
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1645,55 +1694,58 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-653800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-630900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-764200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-779500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-472600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-530100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-220400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-81300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1045700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-524400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-261700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-748000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-311300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-200</v>
       </c>
-      <c r="Q26" s="3">
-        <v>0</v>
-      </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
+      <c r="R26" s="3">
+        <v>0</v>
       </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
@@ -1701,55 +1753,58 @@
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-653800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-630900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-764200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-779500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1726900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-530100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-220400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-81300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1045700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-524400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-261700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2915300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-297500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-200</v>
       </c>
-      <c r="Q27" s="3">
-        <v>0</v>
-      </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
+      <c r="R27" s="3">
+        <v>0</v>
       </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
@@ -1757,8 +1812,11 @@
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1813,8 +1871,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1869,8 +1930,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1925,8 +1989,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1981,50 +2048,53 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-90800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-123500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-75200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>6000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-278200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-158400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-339000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-516700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>559900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>24500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>12700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>449100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>111400</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2037,55 +2107,58 @@
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-653800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-630900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-764200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-779500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1726900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-530100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-220400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-81300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1045700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-524400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-261700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2915300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-297500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-200</v>
       </c>
-      <c r="Q33" s="3">
-        <v>0</v>
-      </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
+      <c r="R33" s="3">
+        <v>0</v>
       </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
@@ -2093,8 +2166,11 @@
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2149,55 +2225,58 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-653800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-630900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-764200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-779500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1726900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-530100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-220400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-81300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1045700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-524400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-261700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2915300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-297500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-200</v>
       </c>
-      <c r="Q35" s="3">
-        <v>0</v>
-      </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
+      <c r="R35" s="3">
+        <v>0</v>
       </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
@@ -2205,69 +2284,75 @@
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2288,8 +2373,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2310,93 +2396,97 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1369900</v>
+      </c>
+      <c r="E41" s="3">
         <v>1164400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2775300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>900000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1735800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1264100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3157400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5391800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6262900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4796900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>557900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>810000</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P41" s="3">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3">
         <v>4200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>200</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2489800</v>
+      </c>
+      <c r="E42" s="3">
         <v>3258200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2474000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2078400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2177200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2078000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1136600</v>
       </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K42" s="3">
-        <v>0</v>
+      <c r="K42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L42" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="M42" s="3">
         <v>500</v>
@@ -2404,8 +2494,8 @@
       <c r="N42" s="3">
         <v>500</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
+      <c r="O42" s="3">
+        <v>500</v>
       </c>
       <c r="P42" s="3" t="s">
         <v>3</v>
@@ -2416,53 +2506,56 @@
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S42" s="3">
-        <v>0</v>
+      <c r="S42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>51800</v>
+      </c>
+      <c r="E43" s="3">
         <v>23400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>20600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>19500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>27700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>27900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>600</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2472,53 +2565,56 @@
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S43" s="3">
-        <v>0</v>
+      <c r="S43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>696200</v>
+      </c>
+      <c r="E44" s="3">
         <v>799000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>849800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1017600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>834400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>685300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>553000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>333900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>127300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>61200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>28200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>6300</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2528,59 +2624,62 @@
       <c r="R44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S44" s="3">
-        <v>0</v>
+      <c r="S44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>149400</v>
+      </c>
+      <c r="E45" s="3">
         <v>146600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>137300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>121300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>145100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>126300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>118100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>137800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>113700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>100600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>67900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>51200</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3">
         <v>1100</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2590,88 +2689,94 @@
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4757200</v>
+      </c>
+      <c r="E46" s="3">
         <v>5391500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6256900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4119800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4912000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4156400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4966500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5864400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6507000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4986800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>682400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>868600</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P46" s="3">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q46" s="3">
         <v>5300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>200</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>461000</v>
+      </c>
+      <c r="E47" s="3">
         <v>479700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>288100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>441700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>530000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>513700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>278100</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2687,12 +2792,12 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3">
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="3">
         <v>2070200</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2702,47 +2807,50 @@
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3032400</v>
+      </c>
+      <c r="E48" s="3">
         <v>2894700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2698500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2536100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2381900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2166200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1813600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1494200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1344100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1109700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1014400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>899900</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2752,14 +2860,17 @@
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S48" s="3">
-        <v>0</v>
+      <c r="S48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2814,8 +2925,11 @@
       <c r="T49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2870,8 +2984,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2926,64 +3043,70 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>262200</v>
+      </c>
+      <c r="E52" s="3">
         <v>175300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>171600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>163300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>55300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>51500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>71200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>43200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>30600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>42700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>39300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>31300</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P52" s="3">
-        <v>0</v>
+      <c r="P52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3">
         <v>200</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3038,64 +3161,70 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8512700</v>
+      </c>
+      <c r="E54" s="3">
         <v>8941200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>9415100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7260900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7879200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6887800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7129400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7401800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7881700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6139200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1736100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1799800</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P54" s="3">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="3">
         <v>2075500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>400</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3116,8 +3245,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3138,55 +3268,56 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>108700</v>
+      </c>
+      <c r="E57" s="3">
         <v>104600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>140100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>145700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>229100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>79800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>129100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>66400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>41300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>8900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>14000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>9200</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P57" s="3">
-        <v>0</v>
+      <c r="P57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q57" s="3">
         <v>0</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
+      <c r="R57" s="3">
+        <v>0</v>
       </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
@@ -3194,215 +3325,227 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>80700</v>
+      </c>
+      <c r="E58" s="3">
         <v>61500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>23500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>19800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>20200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>25500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>7100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>8900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>19500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>27900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>10800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2500</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R58" s="3">
         <v>300</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>819000</v>
+      </c>
+      <c r="E59" s="3">
         <v>871800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>722000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>849400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>688300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>719800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>517900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>436600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>335300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>232600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>175000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>247300</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3">
         <v>100</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1008400</v>
+      </c>
+      <c r="E60" s="3">
         <v>1037900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>885600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1015000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>937600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>825100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>654100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>511900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>396100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>269400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>199800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>259100</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P60" s="3">
-        <v>0</v>
+      <c r="P60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q60" s="3">
+        <v>0</v>
+      </c>
+      <c r="R60" s="3">
         <v>400</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2074600</v>
+      </c>
+      <c r="E61" s="3">
         <v>2072700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2073500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2072000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2073200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2069900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1994600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1994100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1992900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4200</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3418,53 +3561,56 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>578000</v>
+      </c>
+      <c r="E62" s="3">
         <v>424700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>496100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>542200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>518800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>761500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>770400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1066300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1583400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1019900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>164800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1309500</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P62" s="3">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3">
         <v>72500</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3474,8 +3620,11 @@
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3530,8 +3679,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3586,8 +3738,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3642,64 +3797,70 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3661000</v>
+      </c>
+      <c r="E66" s="3">
         <v>3535200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3455200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3629100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3529500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3656600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3419000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3572400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3972400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1294000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>368500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1572800</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P66" s="3">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="3">
         <v>72500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>400</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3720,8 +3881,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3776,8 +3938,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3832,8 +3997,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3865,14 +4033,14 @@
         <v>0</v>
       </c>
       <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3">
         <v>5836800</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>4454800</v>
       </c>
-      <c r="O70" s="3">
-        <v>0</v>
-      </c>
       <c r="P70" s="3">
         <v>0</v>
       </c>
@@ -3888,8 +4056,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3944,55 +4115,58 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-10198800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-9545000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-8914100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-8149900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-7370300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-6897700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-6367600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-6147200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-6065900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-5020200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-4495800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-4234100</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P72" s="3">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3">
         <v>-200</v>
       </c>
-      <c r="Q72" s="3">
-        <v>0</v>
-      </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
+      <c r="R72" s="3">
+        <v>0</v>
       </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
@@ -4000,8 +4174,11 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4056,8 +4233,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4112,8 +4292,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4168,55 +4351,58 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4851700</v>
+      </c>
+      <c r="E76" s="3">
         <v>5406000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5959800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3631900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4349700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3231200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3710400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3829500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3909400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4845200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-4469200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-4227900</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P76" s="3">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3">
         <v>2003000</v>
       </c>
-      <c r="Q76" s="3">
-        <v>0</v>
-      </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
+      <c r="R76" s="3">
+        <v>0</v>
       </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
@@ -4224,8 +4410,11 @@
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4280,116 +4469,122 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-653800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-630900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-764200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-779500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1726900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-530100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-220400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-81300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1045700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-524400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-261700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2915300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-297500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-200</v>
       </c>
-      <c r="Q81" s="3">
-        <v>0</v>
-      </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
+      <c r="R81" s="3">
+        <v>0</v>
       </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
@@ -4397,8 +4592,11 @@
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4419,55 +4617,56 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>67500</v>
+      </c>
+      <c r="E83" s="3">
         <v>60800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>55400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>49800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>55200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>50700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>42400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>38200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>36300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>14900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>6800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4800</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R83" s="3">
-        <v>0</v>
+      <c r="R83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S83" s="3">
         <v>0</v>
@@ -4475,8 +4674,11 @@
       <c r="T83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4531,8 +4733,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4587,8 +4792,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4643,8 +4851,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4699,8 +4910,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4755,55 +4969,58 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-474500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-513600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-700400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-801300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-648500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-569500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-513600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-494600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-312700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-291600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-235100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-218700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-192800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
+      <c r="R89" s="3">
+        <v>0</v>
       </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
@@ -4811,8 +5028,11 @@
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4833,55 +5053,56 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-272600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-192500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-203700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-241800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-289900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-290100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-309800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-185100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-121900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-92800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-111800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-94800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-103700</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
+      <c r="R91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S91" s="3">
         <v>0</v>
@@ -4889,8 +5110,11 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4945,8 +5169,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5001,50 +5228,53 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>652200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1132400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-438000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-28700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-392700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1374900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1729000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-185100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-121400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-92800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-111700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-94800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-103700</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5057,8 +5287,11 @@
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5079,8 +5312,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5135,8 +5369,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5191,8 +5428,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5247,8 +5487,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5303,64 +5546,70 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E100" s="3">
         <v>35100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>3013600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-5700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1512800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>17600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>4100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-187300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1899600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>4624700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>101000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>511100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>398000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2075400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>200</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5415,60 +5664,66 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>205600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1610900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1875300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-835700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>471600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1926700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2238600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-867000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1465500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>4240400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-245800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>197600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>101500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>4000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>200</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LCID_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LCID_QTR_FIN.xlsx
@@ -656,202 +656,208 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>172700</v>
+      </c>
+      <c r="E8" s="3">
         <v>157200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>137800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>150900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>149400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>257700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>195500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>97300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>57700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>26400</v>
-      </c>
-      <c r="M8" s="3">
-        <v>200</v>
       </c>
       <c r="N8" s="3">
         <v>200</v>
       </c>
       <c r="O8" s="3">
+        <v>200</v>
+      </c>
+      <c r="P8" s="3">
         <v>300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3600</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T8" s="3">
-        <v>0</v>
+      <c r="T8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>404800</v>
+      </c>
+      <c r="E9" s="3">
         <v>410000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>469700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>555800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>500500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>615300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>492500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>292300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>246000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>151500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3300</v>
       </c>
-      <c r="N9" s="3">
-        <v>0</v>
-      </c>
       <c r="O9" s="3">
+        <v>0</v>
+      </c>
+      <c r="P9" s="3">
         <v>100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2500</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
@@ -864,53 +870,56 @@
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-232100</v>
+      </c>
+      <c r="E10" s="3">
         <v>-252800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-331900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-404900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-351100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-357600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-297000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-195000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-188300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-125100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-3100</v>
-      </c>
-      <c r="N10" s="3">
-        <v>200</v>
       </c>
       <c r="O10" s="3">
         <v>200</v>
       </c>
       <c r="P10" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q10" s="3">
         <v>1100</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
@@ -923,8 +932,11 @@
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -946,53 +958,54 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>284600</v>
+      </c>
+      <c r="E12" s="3">
         <v>243000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>230800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>233500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>229800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>221300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>213800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>200400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>186100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>163600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>242400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>176800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>167400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>169500</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1005,8 +1018,11 @@
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1064,8 +1080,11 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1073,35 +1092,35 @@
         <v>0</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>22500</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
         <v>0</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
+      <c r="J14" s="3">
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>2700</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1117,14 +1136,17 @@
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1182,8 +1204,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1202,58 +1227,59 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>902700</v>
+      </c>
+      <c r="E17" s="3">
         <v>894000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>890700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>988600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>921600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1007500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>883000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>656500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>655200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>512100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>500000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>249100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>299100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>203300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>300</v>
       </c>
-      <c r="R17" s="3">
-        <v>0</v>
-      </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
+      <c r="S17" s="3">
+        <v>0</v>
       </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
@@ -1261,53 +1287,56 @@
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-730000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-736800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-752900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-837700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-772200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-749800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-687500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-559200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-597500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-485700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-499800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-248900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-298800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-199700</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1320,8 +1349,11 @@
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1343,53 +1375,54 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>56800</v>
+      </c>
+      <c r="E20" s="3">
         <v>90800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>123500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>75200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-6000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>278200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>158400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>339000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>516700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-559900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-24500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-12700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-449100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-111400</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1402,53 +1435,56 @@
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-604300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-578500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-568600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-707100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-728300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-416300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-478400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-177800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-42600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1009200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-509400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-254800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-743000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-306400</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1461,16 +1497,19 @@
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E22" s="3">
         <v>7800</v>
-      </c>
-      <c r="E22" s="3">
-        <v>1200</v>
       </c>
       <c r="F22" s="3">
         <v>1200</v>
@@ -1479,13 +1518,13 @@
         <v>1200</v>
       </c>
       <c r="H22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I22" s="3">
         <v>1300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>900</v>
-      </c>
-      <c r="J22" s="3">
-        <v>100</v>
       </c>
       <c r="K22" s="3">
         <v>100</v>
@@ -1503,10 +1542,10 @@
         <v>100</v>
       </c>
       <c r="P22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>0</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>3</v>
@@ -1520,58 +1559,61 @@
       <c r="U22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-680700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-653800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-630600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-763600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-779400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-472800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-530000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-220400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-81000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1045700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-524400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-261700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-747900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-311200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-200</v>
       </c>
-      <c r="R23" s="3">
-        <v>0</v>
-      </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
+      <c r="S23" s="3">
+        <v>0</v>
       </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
@@ -1579,38 +1621,41 @@
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-200</v>
-      </c>
-      <c r="I24" s="3">
-        <v>100</v>
       </c>
       <c r="J24" s="3">
         <v>100</v>
       </c>
       <c r="K24" s="3">
+        <v>100</v>
+      </c>
+      <c r="L24" s="3">
         <v>300</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
         <v>0</v>
       </c>
@@ -1621,16 +1666,16 @@
         <v>0</v>
       </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>100</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
         <v>0</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
+      <c r="S24" s="3">
+        <v>0</v>
       </c>
       <c r="T24" s="3" t="s">
         <v>3</v>
@@ -1638,8 +1683,11 @@
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1697,58 +1745,61 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-680900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-653800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-630900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-764200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-779500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-472600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-530100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-220400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-81300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1045700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-524400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-261700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-748000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-311300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-200</v>
       </c>
-      <c r="R26" s="3">
-        <v>0</v>
-      </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
+      <c r="S26" s="3">
+        <v>0</v>
       </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
@@ -1756,58 +1807,61 @@
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-684800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-653800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-630900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-764200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-779500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1726900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-530100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-220400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-81300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1045700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-524400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-261700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2915300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-297500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-200</v>
       </c>
-      <c r="R27" s="3">
-        <v>0</v>
-      </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
+      <c r="S27" s="3">
+        <v>0</v>
       </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
@@ -1815,8 +1869,11 @@
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1874,8 +1931,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1933,8 +1993,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1992,8 +2055,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2051,53 +2117,56 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-56800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-90800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-123500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-75200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>6000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-278200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-158400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-339000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-516700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>559900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>24500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>12700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>449100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>111400</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2110,58 +2179,61 @@
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-684800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-653800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-630900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-764200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-779500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1726900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-530100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-220400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-81300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1045700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-524400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-261700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2915300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-297500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-200</v>
       </c>
-      <c r="R33" s="3">
-        <v>0</v>
-      </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
+      <c r="S33" s="3">
+        <v>0</v>
       </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
@@ -2169,8 +2241,11 @@
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2228,58 +2303,61 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-684800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-653800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-630900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-764200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-779500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1726900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-530100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-220400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-81300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1045700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-524400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-261700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2915300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-297500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-200</v>
       </c>
-      <c r="R35" s="3">
-        <v>0</v>
-      </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
+      <c r="S35" s="3">
+        <v>0</v>
       </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
@@ -2287,72 +2365,78 @@
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2374,8 +2458,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2397,99 +2482,103 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2169500</v>
+      </c>
+      <c r="E41" s="3">
         <v>1369900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1164400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2775300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>900000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1735800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1264100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3157400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5391800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6262900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4796900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>557900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>810000</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q41" s="3">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R41" s="3">
         <v>4200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>200</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1824900</v>
+      </c>
+      <c r="E42" s="3">
         <v>2489800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>3258200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2474000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2078400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2177200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2078000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1136600</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L42" s="3">
-        <v>0</v>
+      <c r="L42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M42" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="N42" s="3">
         <v>500</v>
@@ -2497,8 +2586,8 @@
       <c r="O42" s="3">
         <v>500</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
+      <c r="P42" s="3">
+        <v>500</v>
       </c>
       <c r="Q42" s="3" t="s">
         <v>3</v>
@@ -2509,56 +2598,59 @@
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T42" s="3">
-        <v>0</v>
+      <c r="T42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>126900</v>
+      </c>
+      <c r="E43" s="3">
         <v>51800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>23400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>20600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>19500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>27700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>27900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>600</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2568,56 +2660,59 @@
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T43" s="3">
-        <v>0</v>
+      <c r="T43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>565700</v>
+      </c>
+      <c r="E44" s="3">
         <v>696200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>799000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>849800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1017600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>834400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>685300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>553000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>333900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>127300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>61200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>28200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>6300</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2627,62 +2722,65 @@
       <c r="S44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T44" s="3">
-        <v>0</v>
+      <c r="T44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>147000</v>
+      </c>
+      <c r="E45" s="3">
         <v>149400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>146600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>137300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>121300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>145100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>126300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>118100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>137800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>113700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>100600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>67900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>51200</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3">
         <v>1100</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2692,94 +2790,100 @@
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4834000</v>
+      </c>
+      <c r="E46" s="3">
         <v>4757200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5391500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6256900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4119800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4912000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4156400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4966500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5864400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6507000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4986800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>682400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>868600</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q46" s="3">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R46" s="3">
         <v>5300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>200</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>688400</v>
+      </c>
+      <c r="E47" s="3">
         <v>461000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>479700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>288100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>441700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>530000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>513700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>278100</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2795,12 +2899,12 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R47" s="3">
         <v>2070200</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2810,50 +2914,53 @@
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3189300</v>
+      </c>
+      <c r="E48" s="3">
         <v>3032400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2894700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2698500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2536100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2381900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2166200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1813600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1494200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1344100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1109700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1014400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>899900</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2863,14 +2970,17 @@
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T48" s="3">
-        <v>0</v>
+      <c r="T48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2928,8 +3038,11 @@
       <c r="U49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2987,8 +3100,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3046,67 +3162,73 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>185400</v>
+      </c>
+      <c r="E52" s="3">
         <v>262200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>175300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>171600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>163300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>55300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>51500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>71200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>43200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>30600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>42700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>39300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>31300</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>0</v>
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R52" s="3">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3">
         <v>200</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3164,67 +3286,73 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8897000</v>
+      </c>
+      <c r="E54" s="3">
         <v>8512700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8941200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>9415100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7260900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7879200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6887800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7129400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7401800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7881700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6139200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1736100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1799800</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q54" s="3">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R54" s="3">
         <v>2075500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>400</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3246,8 +3374,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3269,58 +3398,59 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>101500</v>
+      </c>
+      <c r="E57" s="3">
         <v>108700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>104600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>140100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>145700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>229100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>79800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>129100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>66400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>41300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>8900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>14000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>9200</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>0</v>
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R57" s="3">
         <v>0</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
+      <c r="S57" s="3">
+        <v>0</v>
       </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
@@ -3328,227 +3458,239 @@
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>80100</v>
+      </c>
+      <c r="E58" s="3">
         <v>80700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>61500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>23500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>19800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>20200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>25500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>7100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>8900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>19500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>27900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>10800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2500</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R58" s="3">
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S58" s="3">
         <v>300</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>855200</v>
+      </c>
+      <c r="E59" s="3">
         <v>819000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>871800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>722000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>849400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>688300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>719800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>517900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>436600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>335300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>232600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>175000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>247300</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R59" s="3">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S59" s="3">
         <v>100</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1036700</v>
+      </c>
+      <c r="E60" s="3">
         <v>1008400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1037900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>885600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1015000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>937600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>825100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>654100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>511900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>396100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>269400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>199800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>259100</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>0</v>
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R60" s="3">
+        <v>0</v>
+      </c>
+      <c r="S60" s="3">
         <v>400</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2074100</v>
+      </c>
+      <c r="E61" s="3">
         <v>2074600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2072700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2073500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2072000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2073200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2069900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1994600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1994100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1992900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4200</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3564,56 +3706,59 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1049600</v>
+      </c>
+      <c r="E62" s="3">
         <v>578000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>424700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>496100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>542200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>518800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>761500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>770400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1066300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1583400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1019900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>164800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1309500</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q62" s="3">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R62" s="3">
         <v>72500</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3623,8 +3768,11 @@
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3682,8 +3830,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3741,8 +3892,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3800,67 +3954,73 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4160400</v>
+      </c>
+      <c r="E66" s="3">
         <v>3661000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3535200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3455200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3629100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3529500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3656600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3419000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3572400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3972400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1294000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>368500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1572800</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q66" s="3">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R66" s="3">
         <v>72500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>400</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3882,8 +4042,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3941,8 +4102,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4000,13 +4164,16 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>0</v>
+        <v>504500</v>
       </c>
       <c r="E70" s="3">
         <v>0</v>
@@ -4036,14 +4203,14 @@
         <v>0</v>
       </c>
       <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
         <v>5836800</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>4454800</v>
       </c>
-      <c r="P70" s="3">
-        <v>0</v>
-      </c>
       <c r="Q70" s="3">
         <v>0</v>
       </c>
@@ -4059,8 +4226,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4118,58 +4288,61 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-10879600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-10198800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-9545000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-8914100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-8149900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-7370300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-6897700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-6367600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-6147200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-6065900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-5020200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-4495800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-4234100</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q72" s="3">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R72" s="3">
         <v>-200</v>
       </c>
-      <c r="R72" s="3">
-        <v>0</v>
-      </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
+      <c r="S72" s="3">
+        <v>0</v>
       </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
@@ -4177,8 +4350,11 @@
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4236,8 +4412,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4295,8 +4474,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4354,58 +4536,61 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4232200</v>
+      </c>
+      <c r="E76" s="3">
         <v>4851700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5406000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5959800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3631900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4349700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3231200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3710400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3829500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3909400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4845200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-4469200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-4227900</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q76" s="3">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R76" s="3">
         <v>2003000</v>
       </c>
-      <c r="R76" s="3">
-        <v>0</v>
-      </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
+      <c r="S76" s="3">
+        <v>0</v>
       </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
@@ -4413,8 +4598,11 @@
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4472,122 +4660,128 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-684800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-653800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-630900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-764200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-779500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1726900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-530100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-220400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-81300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1045700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-524400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-261700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2915300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-297500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-200</v>
       </c>
-      <c r="R81" s="3">
-        <v>0</v>
-      </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
+      <c r="S81" s="3">
+        <v>0</v>
       </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
@@ -4595,8 +4789,11 @@
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4618,58 +4815,59 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>68800</v>
+      </c>
+      <c r="E83" s="3">
         <v>67500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>60800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>55400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>49800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>55200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>50700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>42400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>38200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>36300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>14900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>6800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4800</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S83" s="3">
-        <v>0</v>
+      <c r="S83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T83" s="3">
         <v>0</v>
@@ -4677,8 +4875,11 @@
       <c r="U83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4736,8 +4937,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4795,8 +4999,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4854,8 +5061,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4913,8 +5123,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4972,58 +5185,61 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-516700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-474500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-513600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-700400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-801300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-648500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-569500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-513600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-494600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-312700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-291600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-235100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-218700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-192800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1400</v>
       </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
+      <c r="S89" s="3">
+        <v>0</v>
       </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
@@ -5031,8 +5247,11 @@
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5054,58 +5273,59 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-198200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-272600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-192500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-203700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-241800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-289900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-290100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-309800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-185100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-121900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-92800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-111800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-94800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-103700</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
+      <c r="S91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T91" s="3">
         <v>0</v>
@@ -5113,8 +5333,11 @@
       <c r="U91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5172,8 +5395,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5231,53 +5457,56 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>317500</v>
+      </c>
+      <c r="E94" s="3">
         <v>652200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1132400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-438000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-28700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-392700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1374900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1729000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-185100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-121400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-92800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-111700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-94800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-103700</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5290,8 +5519,11 @@
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5313,8 +5545,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5372,8 +5605,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5431,8 +5667,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5490,8 +5729,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5549,67 +5791,73 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>997200</v>
+      </c>
+      <c r="E100" s="3">
         <v>28000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>35100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>3013600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-5700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1512800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>17600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>4100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-187300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1899600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>4624700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>101000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>511100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>398000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2075400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>200</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5667,63 +5915,69 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>798000</v>
+      </c>
+      <c r="E102" s="3">
         <v>205600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1610900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1875300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-835700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>471600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1926700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2238600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-867000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1465500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>4240400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-245800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>197600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>101500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>4000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>200</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LCID_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LCID_QTR_FIN.xlsx
@@ -656,211 +656,217 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="6" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>200600</v>
+      </c>
+      <c r="E8" s="3">
         <v>172700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>157200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>137800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>150900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>149400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>257700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>195500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>97300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>57700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>26400</v>
-      </c>
-      <c r="N8" s="3">
-        <v>200</v>
       </c>
       <c r="O8" s="3">
         <v>200</v>
       </c>
       <c r="P8" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q8" s="3">
         <v>300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3600</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U8" s="3">
-        <v>0</v>
+      <c r="U8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>470400</v>
+      </c>
+      <c r="E9" s="3">
         <v>404800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>410000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>469700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>555800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>500500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>615300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>492500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>292300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>246000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>151500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3300</v>
       </c>
-      <c r="O9" s="3">
-        <v>0</v>
-      </c>
       <c r="P9" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="3">
         <v>100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2500</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
@@ -873,56 +879,59 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-269800</v>
+      </c>
+      <c r="E10" s="3">
         <v>-232100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-252800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-331900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-404900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-351100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-357600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-297000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-195000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-188300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-125100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-3100</v>
-      </c>
-      <c r="O10" s="3">
-        <v>200</v>
       </c>
       <c r="P10" s="3">
         <v>200</v>
       </c>
       <c r="Q10" s="3">
+        <v>200</v>
+      </c>
+      <c r="R10" s="3">
         <v>1100</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
@@ -935,8 +944,11 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -959,56 +971,57 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>287200</v>
+      </c>
+      <c r="E12" s="3">
         <v>284600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>243000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>230800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>233500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>229800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>221300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>213800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>200400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>186100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>163600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>242400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>176800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>167400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>169500</v>
       </c>
-      <c r="R12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1021,8 +1034,11 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1083,47 +1099,50 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>20200</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
       </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>22500</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
         <v>0</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
+      <c r="K14" s="3">
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>2700</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1139,14 +1158,17 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1207,8 +1229,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1228,61 +1253,62 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>988000</v>
+      </c>
+      <c r="E17" s="3">
         <v>902700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>894000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>890700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>988600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>921600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1007500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>883000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>656500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>655200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>512100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>500000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>249100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>299100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>203300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>300</v>
       </c>
-      <c r="S17" s="3">
-        <v>0</v>
-      </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
+      <c r="T17" s="3">
+        <v>0</v>
       </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
@@ -1290,56 +1316,59 @@
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-787400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-730000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-736800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-752900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-837700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-772200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-749800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-687500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-559200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-597500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-485700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-499800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-248900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-298800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-199700</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1352,8 +1381,11 @@
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1376,56 +1408,57 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>150600</v>
+      </c>
+      <c r="E20" s="3">
         <v>56800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>90800</v>
       </c>
-      <c r="F20" s="3">
-        <v>123500</v>
-      </c>
       <c r="G20" s="3">
-        <v>75200</v>
+        <v>125600</v>
       </c>
       <c r="H20" s="3">
-        <v>-6000</v>
+        <v>80700</v>
       </c>
       <c r="I20" s="3">
-        <v>278200</v>
+        <v>-100</v>
       </c>
       <c r="J20" s="3">
+        <v>285000</v>
+      </c>
+      <c r="K20" s="3">
         <v>158400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>339000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>516700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-559900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-24500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-12700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-449100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-111400</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1438,56 +1471,59 @@
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-570600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-604300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-578500</v>
       </c>
-      <c r="F21" s="3">
-        <v>-568600</v>
-      </c>
       <c r="G21" s="3">
-        <v>-707100</v>
+        <v>-566400</v>
       </c>
       <c r="H21" s="3">
-        <v>-728300</v>
+        <v>-701600</v>
       </c>
       <c r="I21" s="3">
-        <v>-416300</v>
+        <v>-722500</v>
       </c>
       <c r="J21" s="3">
+        <v>-409500</v>
+      </c>
+      <c r="K21" s="3">
         <v>-478400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-177800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-42600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1009200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-509400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-254800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-743000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-306400</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1500,34 +1536,37 @@
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E22" s="3">
         <v>7500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>7800</v>
       </c>
-      <c r="F22" s="3">
-        <v>1200</v>
-      </c>
       <c r="G22" s="3">
-        <v>1200</v>
+        <v>3300</v>
       </c>
       <c r="H22" s="3">
-        <v>1200</v>
+        <v>6700</v>
       </c>
       <c r="I22" s="3">
-        <v>1300</v>
+        <v>7100</v>
       </c>
       <c r="J22" s="3">
+        <v>8100</v>
+      </c>
+      <c r="K22" s="3">
         <v>900</v>
-      </c>
-      <c r="K22" s="3">
-        <v>100</v>
       </c>
       <c r="L22" s="3">
         <v>100</v>
@@ -1545,10 +1584,10 @@
         <v>100</v>
       </c>
       <c r="Q22" s="3">
-        <v>0</v>
-      </c>
-      <c r="R22" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="R22" s="3">
+        <v>0</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>3</v>
@@ -1562,61 +1601,64 @@
       <c r="V22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-643500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-680700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-653800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-630600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-763600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-779400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-472800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-530000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-220400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-81000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1045700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-524400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-261700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-747900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-311200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-200</v>
       </c>
-      <c r="S23" s="3">
-        <v>0</v>
-      </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
+      <c r="T23" s="3">
+        <v>0</v>
       </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
@@ -1624,41 +1666,44 @@
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E24" s="3">
         <v>200</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-200</v>
-      </c>
-      <c r="J24" s="3">
-        <v>100</v>
       </c>
       <c r="K24" s="3">
         <v>100</v>
       </c>
       <c r="L24" s="3">
+        <v>100</v>
+      </c>
+      <c r="M24" s="3">
         <v>300</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
         <v>0</v>
       </c>
@@ -1669,16 +1714,16 @@
         <v>0</v>
       </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>100</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
         <v>0</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
+      <c r="T24" s="3">
+        <v>0</v>
       </c>
       <c r="U24" s="3" t="s">
         <v>3</v>
@@ -1686,8 +1731,11 @@
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1748,61 +1796,64 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-643400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-680900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-653800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-630900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-764200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-779500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-472600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-530100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-220400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-81300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1045700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-524400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-261700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-748000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-311300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-200</v>
       </c>
-      <c r="S26" s="3">
-        <v>0</v>
-      </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
+      <c r="T26" s="3">
+        <v>0</v>
       </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
@@ -1810,61 +1861,64 @@
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-790300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-684800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-653800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-630900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-764200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-779500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1726900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-530100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-220400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-81300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1045700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-524400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-261700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2915300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-297500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-200</v>
       </c>
-      <c r="S27" s="3">
-        <v>0</v>
-      </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
+      <c r="T27" s="3">
+        <v>0</v>
       </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
@@ -1872,8 +1926,11 @@
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1934,8 +1991,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1996,8 +2056,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2058,8 +2121,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2120,56 +2186,59 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-150600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-56800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-90800</v>
       </c>
-      <c r="F32" s="3">
-        <v>-123500</v>
-      </c>
       <c r="G32" s="3">
-        <v>-75200</v>
+        <v>-125600</v>
       </c>
       <c r="H32" s="3">
-        <v>6000</v>
+        <v>-80700</v>
       </c>
       <c r="I32" s="3">
-        <v>-278200</v>
+        <v>100</v>
       </c>
       <c r="J32" s="3">
+        <v>-285000</v>
+      </c>
+      <c r="K32" s="3">
         <v>-158400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-339000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-516700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>559900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>24500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>12700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>449100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>111400</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2182,61 +2251,64 @@
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-790300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-684800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-653800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-630900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-764200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-779500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1726900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-530100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-220400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-81300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1045700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-524400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-261700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2915300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-297500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-200</v>
       </c>
-      <c r="S33" s="3">
-        <v>0</v>
-      </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
+      <c r="T33" s="3">
+        <v>0</v>
       </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
@@ -2244,8 +2316,11 @@
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2306,61 +2381,64 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-790300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-684800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-653800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-630900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-764200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-779500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1726900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-530100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-220400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-81300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1045700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-524400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-261700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2915300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-297500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-200</v>
       </c>
-      <c r="S35" s="3">
-        <v>0</v>
-      </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
+      <c r="T35" s="3">
+        <v>0</v>
       </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
@@ -2368,75 +2446,81 @@
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2459,8 +2543,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2483,105 +2568,109 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1353600</v>
+      </c>
+      <c r="E41" s="3">
         <v>2169500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1369900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1164400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2775300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>900000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1735800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1264100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3157400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5391800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6262900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4796900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>557900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>810000</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R41" s="3">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S41" s="3">
         <v>4200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>200</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1862800</v>
+      </c>
+      <c r="E42" s="3">
         <v>1824900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2489800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>3258200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2474000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2078400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2177200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>2078000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1136600</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M42" s="3">
-        <v>0</v>
+      <c r="M42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N42" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="O42" s="3">
         <v>500</v>
@@ -2589,8 +2678,8 @@
       <c r="P42" s="3">
         <v>500</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>3</v>
+      <c r="Q42" s="3">
+        <v>500</v>
       </c>
       <c r="R42" s="3" t="s">
         <v>3</v>
@@ -2601,59 +2690,62 @@
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U42" s="3">
-        <v>0</v>
+      <c r="U42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>101400</v>
+      </c>
+      <c r="E43" s="3">
         <v>126900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>51800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>23400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>20600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>19500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>27700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>27900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>600</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2663,59 +2755,62 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U43" s="3">
-        <v>0</v>
+      <c r="U43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>509900</v>
+      </c>
+      <c r="E44" s="3">
         <v>565700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>696200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>799000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>849800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1017600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>834400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>685300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>553000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>333900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>127300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>61200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>28200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>6300</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2725,65 +2820,68 @@
       <c r="T44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U44" s="3">
-        <v>0</v>
+      <c r="U44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>173800</v>
+      </c>
+      <c r="E45" s="3">
         <v>147000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>149400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>146600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>137300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>121300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>145100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>126300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>118100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>137800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>113700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>100600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>67900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>51200</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R45" s="3">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S45" s="3">
         <v>1100</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2793,100 +2891,106 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4001500</v>
+      </c>
+      <c r="E46" s="3">
         <v>4834000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4757200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5391500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6256900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4119800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4912000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4156400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4966500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5864400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6507000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4986800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>682400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>868600</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R46" s="3">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S46" s="3">
         <v>5300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>200</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>739100</v>
+      </c>
+      <c r="E47" s="3">
         <v>688400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>461000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>479700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>288100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>441700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>530000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>513700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>278100</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2902,12 +3006,12 @@
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R47" s="3">
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S47" s="3">
         <v>2070200</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2917,53 +3021,56 @@
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3278600</v>
+      </c>
+      <c r="E48" s="3">
         <v>3189300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3032400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2894700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2698500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2536100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2381900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2166200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1813600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1494200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1344100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1109700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1014400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>899900</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2973,14 +3080,17 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U48" s="3">
-        <v>0</v>
+      <c r="U48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3041,8 +3151,11 @@
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3103,8 +3216,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3165,70 +3281,76 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>204000</v>
+      </c>
+      <c r="E52" s="3">
         <v>185400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>262200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>175300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>171600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>163300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>55300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>51500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>71200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>43200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>30600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>42700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>39300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>31300</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R52" s="3">
-        <v>0</v>
+      <c r="R52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S52" s="3">
+        <v>0</v>
+      </c>
+      <c r="T52" s="3">
         <v>200</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3289,70 +3411,76 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8223300</v>
+      </c>
+      <c r="E54" s="3">
         <v>8897000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8512700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8941200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>9415100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7260900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7879200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6887800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7129400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7401800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7881700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6139200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1736100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1799800</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R54" s="3">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S54" s="3">
         <v>2075500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>400</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3375,8 +3503,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3399,61 +3528,62 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>113600</v>
+      </c>
+      <c r="E57" s="3">
         <v>101500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>108700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>104600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>140100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>145700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>229100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>79800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>129100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>66400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>41300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>8900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>14000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>9200</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R57" s="3">
-        <v>0</v>
+      <c r="R57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S57" s="3">
         <v>0</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
+      <c r="T57" s="3">
+        <v>0</v>
       </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
@@ -3461,239 +3591,251 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>75300</v>
+      </c>
+      <c r="E58" s="3">
         <v>80100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>80700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>61500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>23500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>19800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>20200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>25500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>7100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>8900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>19500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>27900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>10800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2500</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S58" s="3">
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T58" s="3">
         <v>300</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>821900</v>
+      </c>
+      <c r="E59" s="3">
         <v>855200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>819000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>871800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>722000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>849400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>688300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>719800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>517900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>436600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>335300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>232600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>175000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>247300</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S59" s="3">
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T59" s="3">
         <v>100</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1010900</v>
+      </c>
+      <c r="E60" s="3">
         <v>1036700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1008400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1037900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>885600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1015000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>937600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>825100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>654100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>511900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>396100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>269400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>199800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>259100</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R60" s="3">
-        <v>0</v>
+      <c r="R60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S60" s="3">
+        <v>0</v>
+      </c>
+      <c r="T60" s="3">
         <v>400</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2076100</v>
+      </c>
+      <c r="E61" s="3">
         <v>2074100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2074600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2072700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2073500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2072000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2073200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2069900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1994600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1994100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1992900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4200</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3709,59 +3851,62 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>969100</v>
+      </c>
+      <c r="E62" s="3">
         <v>1049600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>578000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>424700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>496100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>542200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>518800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>761500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>770400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1066300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1583400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1019900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>164800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1309500</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R62" s="3">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S62" s="3">
         <v>72500</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3771,8 +3916,11 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3833,8 +3981,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3895,8 +4046,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3957,70 +4111,76 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4056100</v>
+      </c>
+      <c r="E66" s="3">
         <v>4160400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3661000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3535200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3455200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3629100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3529500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3656600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3419000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3572400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3972400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1294000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>368500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1572800</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R66" s="3">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S66" s="3">
         <v>72500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>400</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4043,8 +4203,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4105,8 +4266,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4167,17 +4331,20 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>651300</v>
+      </c>
+      <c r="E70" s="3">
         <v>504500</v>
       </c>
-      <c r="E70" s="3">
-        <v>0</v>
-      </c>
       <c r="F70" s="3">
         <v>0</v>
       </c>
@@ -4206,14 +4373,14 @@
         <v>0</v>
       </c>
       <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
         <v>5836800</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>4454800</v>
       </c>
-      <c r="Q70" s="3">
-        <v>0</v>
-      </c>
       <c r="R70" s="3">
         <v>0</v>
       </c>
@@ -4229,8 +4396,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4291,61 +4461,64 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-11523000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-10879600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-10198800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-9545000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-8914100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-8149900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-7370300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-6897700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-6367600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-6147200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-6065900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-5020200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-4495800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-4234100</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R72" s="3">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S72" s="3">
         <v>-200</v>
       </c>
-      <c r="S72" s="3">
-        <v>0</v>
-      </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
+      <c r="T72" s="3">
+        <v>0</v>
       </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
@@ -4353,8 +4526,11 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4415,8 +4591,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4477,8 +4656,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4539,61 +4721,64 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3515900</v>
+      </c>
+      <c r="E76" s="3">
         <v>4232200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4851700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5406000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5959800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3631900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4349700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3231200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3710400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3829500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3909400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4845200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-4469200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-4227900</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R76" s="3">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S76" s="3">
         <v>2003000</v>
       </c>
-      <c r="S76" s="3">
-        <v>0</v>
-      </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
+      <c r="T76" s="3">
+        <v>0</v>
       </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
@@ -4601,8 +4786,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4663,128 +4851,134 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-790300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-684800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-653800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-630900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-764200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-779500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1726900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-530100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-220400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-81300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1045700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-524400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-261700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2915300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-297500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-200</v>
       </c>
-      <c r="S81" s="3">
-        <v>0</v>
-      </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
+      <c r="T81" s="3">
+        <v>0</v>
       </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
@@ -4792,8 +4986,11 @@
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4816,61 +5013,62 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>66200</v>
+      </c>
+      <c r="E83" s="3">
         <v>68800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>67500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>60800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>55400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>49800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>55200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>50700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>42400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>38200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>36300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>14900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>6800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4800</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T83" s="3">
-        <v>0</v>
+      <c r="T83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U83" s="3">
         <v>0</v>
@@ -4878,8 +5076,11 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4940,8 +5141,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5002,8 +5206,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5064,8 +5271,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5126,8 +5336,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5188,61 +5401,64 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-507000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-516700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-474500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-513600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-700400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-801300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-648500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-569500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-513600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-494600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-312700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-291600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-235100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-218700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-192800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1400</v>
       </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
+      <c r="T89" s="3">
+        <v>0</v>
       </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
@@ -5250,8 +5466,11 @@
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5274,61 +5493,62 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-234300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-198200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-272600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-192500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-203700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-241800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-289900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-290100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-309800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-185100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-121900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-92800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-111800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-94800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-103700</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
+      <c r="T91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U91" s="3">
         <v>0</v>
@@ -5336,8 +5556,11 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5398,8 +5621,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5460,56 +5686,59 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-311300</v>
+      </c>
+      <c r="E94" s="3">
         <v>317500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>652200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1132400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-438000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-28700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-392700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1374900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1729000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-185100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-121400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-92800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-111700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-94800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-103700</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5522,8 +5751,11 @@
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5546,8 +5778,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5608,8 +5841,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5670,8 +5906,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5732,8 +5971,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5794,70 +6036,76 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E100" s="3">
         <v>997200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>28000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>35100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>3013600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-5700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1512800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>17600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>4100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-187300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1899600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>4624700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>101000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>511100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>398000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2075400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>200</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5918,66 +6166,72 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-815900</v>
+      </c>
+      <c r="E102" s="3">
         <v>798000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>205600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1610900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1875300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-835700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>471600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1926700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2238600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-867000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1465500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>4240400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-245800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>197600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>101500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>4000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>200</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LCID_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LCID_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="92">
   <si>
     <t>LCID</t>
   </si>
@@ -656,220 +656,226 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="7" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>200000</v>
+      </c>
+      <c r="E8" s="3">
         <v>200600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>172700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>157200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>137800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>150900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>149400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>257700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>195500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>97300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>57700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>26400</v>
-      </c>
-      <c r="O8" s="3">
-        <v>200</v>
       </c>
       <c r="P8" s="3">
         <v>200</v>
       </c>
       <c r="Q8" s="3">
+        <v>200</v>
+      </c>
+      <c r="R8" s="3">
         <v>300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3600</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V8" s="3">
-        <v>0</v>
+      <c r="V8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>412500</v>
+      </c>
+      <c r="E9" s="3">
         <v>470400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>404800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>410000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>469700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>555800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>500500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>615300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>492500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>292300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>246000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>151500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3300</v>
       </c>
-      <c r="P9" s="3">
-        <v>0</v>
-      </c>
       <c r="Q9" s="3">
+        <v>0</v>
+      </c>
+      <c r="R9" s="3">
         <v>100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2500</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
@@ -882,59 +888,62 @@
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-212500</v>
+      </c>
+      <c r="E10" s="3">
         <v>-269800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-232100</v>
       </c>
-      <c r="F10" s="3">
-        <v>-252800</v>
-      </c>
       <c r="G10" s="3">
+        <v>-252900</v>
+      </c>
+      <c r="H10" s="3">
         <v>-331900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-404900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-351100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-357600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-297000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-195000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-188300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-125100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-3100</v>
-      </c>
-      <c r="P10" s="3">
-        <v>200</v>
       </c>
       <c r="Q10" s="3">
         <v>200</v>
       </c>
       <c r="R10" s="3">
+        <v>200</v>
+      </c>
+      <c r="S10" s="3">
         <v>1100</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
@@ -947,8 +956,11 @@
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -972,59 +984,60 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>324400</v>
+      </c>
+      <c r="E12" s="3">
         <v>287200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>284600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>243000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>230800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>233500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>229800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>221300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>213800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>200400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>186100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>163600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>242400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>176800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>167400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>169500</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1037,8 +1050,11 @@
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1102,50 +1118,53 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>20200</v>
+        <v>8900</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>29600</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>19900</v>
       </c>
       <c r="G14" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="H14" s="3">
         <v>500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>22500</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>2700</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1161,37 +1180,40 @@
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>69500</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>66200</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>68800</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>67500</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>60800</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>55400</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>49800</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1232,8 +1254,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1254,64 +1279,65 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>988000</v>
+        <v>970500</v>
       </c>
       <c r="E17" s="3">
+        <v>967800</v>
+      </c>
+      <c r="F17" s="3">
         <v>902700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>894000</v>
       </c>
-      <c r="G17" s="3">
-        <v>890700</v>
-      </c>
       <c r="H17" s="3">
-        <v>988600</v>
+        <v>890200</v>
       </c>
       <c r="I17" s="3">
-        <v>921600</v>
+        <v>987000</v>
       </c>
       <c r="J17" s="3">
+        <v>899100</v>
+      </c>
+      <c r="K17" s="3">
         <v>1007500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>883000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>656500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>655200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>512100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>500000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>249100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>299100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>203300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>300</v>
       </c>
-      <c r="T17" s="3">
-        <v>0</v>
-      </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
+      <c r="U17" s="3">
+        <v>0</v>
       </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
@@ -1319,59 +1345,62 @@
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-787400</v>
+        <v>-770500</v>
       </c>
       <c r="E18" s="3">
-        <v>-730000</v>
+        <v>-767200</v>
       </c>
       <c r="F18" s="3">
-        <v>-736800</v>
+        <v>-729900</v>
       </c>
       <c r="G18" s="3">
-        <v>-752900</v>
+        <v>-736900</v>
       </c>
       <c r="H18" s="3">
-        <v>-837700</v>
+        <v>-752400</v>
       </c>
       <c r="I18" s="3">
-        <v>-772200</v>
+        <v>-836200</v>
       </c>
       <c r="J18" s="3">
+        <v>-749700</v>
+      </c>
+      <c r="K18" s="3">
         <v>-749800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-687500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-559200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-597500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-485700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-499800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-248900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-298800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-199700</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1384,8 +1413,11 @@
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1409,59 +1441,60 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>150600</v>
+        <v>254200</v>
       </c>
       <c r="E20" s="3">
-        <v>56800</v>
+        <v>-105500</v>
       </c>
       <c r="F20" s="3">
-        <v>90800</v>
+        <v>-26000</v>
       </c>
       <c r="G20" s="3">
-        <v>125600</v>
+        <v>-26200</v>
       </c>
       <c r="H20" s="3">
-        <v>80700</v>
+        <v>-59600</v>
       </c>
       <c r="I20" s="3">
-        <v>-100</v>
+        <v>-41200</v>
       </c>
       <c r="J20" s="3">
+        <v>40100</v>
+      </c>
+      <c r="K20" s="3">
         <v>285000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>158400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>339000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>516700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-559900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-24500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-12700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-449100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-111400</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1474,59 +1507,62 @@
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-570600</v>
+        <v>-955100</v>
       </c>
       <c r="E21" s="3">
-        <v>-604300</v>
+        <v>-595500</v>
       </c>
       <c r="F21" s="3">
-        <v>-578500</v>
+        <v>-635000</v>
       </c>
       <c r="G21" s="3">
-        <v>-566400</v>
+        <v>-643200</v>
       </c>
       <c r="H21" s="3">
-        <v>-701600</v>
+        <v>-632000</v>
       </c>
       <c r="I21" s="3">
-        <v>-722500</v>
+        <v>-739600</v>
       </c>
       <c r="J21" s="3">
+        <v>-740000</v>
+      </c>
+      <c r="K21" s="3">
         <v>-409500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-478400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-177800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-42600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1009200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-509400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-254800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-743000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-306400</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1539,37 +1575,40 @@
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E22" s="3">
         <v>6700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>7500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>7800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>3300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>6700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>7100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>8100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>900</v>
-      </c>
-      <c r="L22" s="3">
-        <v>100</v>
       </c>
       <c r="M22" s="3">
         <v>100</v>
@@ -1587,10 +1626,10 @@
         <v>100</v>
       </c>
       <c r="R22" s="3">
-        <v>0</v>
-      </c>
-      <c r="S22" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="S22" s="3">
+        <v>0</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>3</v>
@@ -1604,64 +1643,67 @@
       <c r="W22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-992000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-643500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-680700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-653800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-630600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-763600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-779400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-472800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-530000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-220400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-81000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1045700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-524400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-261700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-747900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-311200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-200</v>
       </c>
-      <c r="T23" s="3">
-        <v>0</v>
-      </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
+      <c r="U23" s="3">
+        <v>0</v>
       </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
@@ -1669,44 +1711,47 @@
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>500</v>
+      </c>
+      <c r="E24" s="3">
         <v>-100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>200</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-200</v>
-      </c>
-      <c r="K24" s="3">
-        <v>100</v>
       </c>
       <c r="L24" s="3">
         <v>100</v>
       </c>
       <c r="M24" s="3">
+        <v>100</v>
+      </c>
+      <c r="N24" s="3">
         <v>300</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
         <v>0</v>
       </c>
@@ -1717,16 +1762,16 @@
         <v>0</v>
       </c>
       <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
         <v>100</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
       <c r="T24" s="3">
         <v>0</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
+      <c r="U24" s="3">
+        <v>0</v>
       </c>
       <c r="V24" s="3" t="s">
         <v>3</v>
@@ -1734,8 +1779,11 @@
       <c r="W24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1799,64 +1847,67 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-992500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-643400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-680900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-653800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-630900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-764200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-779500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-472600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-530100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-220400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-81300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1045700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-524400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-261700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-748000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-311300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-200</v>
       </c>
-      <c r="T26" s="3">
-        <v>0</v>
-      </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
+      <c r="U26" s="3">
+        <v>0</v>
       </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
@@ -1864,64 +1915,67 @@
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-949600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-790300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-684800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-653800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-630900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-764200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-779500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1726900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-530100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-220400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-81300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1045700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-524400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-261700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2915300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-297500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-200</v>
       </c>
-      <c r="T27" s="3">
-        <v>0</v>
-      </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
+      <c r="U27" s="3">
+        <v>0</v>
       </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
@@ -1929,8 +1983,11 @@
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1994,8 +2051,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2059,8 +2119,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2124,8 +2187,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2189,59 +2255,62 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-150600</v>
+        <v>-254200</v>
       </c>
       <c r="E32" s="3">
-        <v>-56800</v>
+        <v>105500</v>
       </c>
       <c r="F32" s="3">
-        <v>-90800</v>
+        <v>26000</v>
       </c>
       <c r="G32" s="3">
-        <v>-125600</v>
+        <v>26200</v>
       </c>
       <c r="H32" s="3">
-        <v>-80700</v>
+        <v>59600</v>
       </c>
       <c r="I32" s="3">
-        <v>100</v>
+        <v>41200</v>
       </c>
       <c r="J32" s="3">
+        <v>-40100</v>
+      </c>
+      <c r="K32" s="3">
         <v>-285000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-158400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-339000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-516700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>559900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>24500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>12700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>449100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>111400</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2254,64 +2323,67 @@
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-790300</v>
+        <v>-992500</v>
       </c>
       <c r="E33" s="3">
-        <v>-684800</v>
+        <v>-643400</v>
       </c>
       <c r="F33" s="3">
+        <v>-680900</v>
+      </c>
+      <c r="G33" s="3">
         <v>-653800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-630900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-764200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-779500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1726900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-530100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-220400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-81300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1045700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-524400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-261700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2915300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-297500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-200</v>
       </c>
-      <c r="T33" s="3">
-        <v>0</v>
-      </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
+      <c r="U33" s="3">
+        <v>0</v>
       </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
@@ -2319,8 +2391,11 @@
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2384,64 +2459,67 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-790300</v>
+        <v>-992500</v>
       </c>
       <c r="E35" s="3">
-        <v>-684800</v>
+        <v>-643400</v>
       </c>
       <c r="F35" s="3">
+        <v>-680900</v>
+      </c>
+      <c r="G35" s="3">
         <v>-653800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-630900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-764200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-779500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1726900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-530100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-220400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-81300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1045700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-524400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-261700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2915300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-297500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-200</v>
       </c>
-      <c r="T35" s="3">
-        <v>0</v>
-      </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
+      <c r="U35" s="3">
+        <v>0</v>
       </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
@@ -2449,78 +2527,84 @@
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2544,8 +2628,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2569,111 +2654,115 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1893600</v>
+      </c>
+      <c r="E41" s="3">
         <v>1353600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2169500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1369900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1164400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2775300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>900000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1735800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1264100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3157400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5391800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6262900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4796900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>557900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>810000</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S41" s="3">
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T41" s="3">
         <v>4200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>200</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1578300</v>
+      </c>
+      <c r="E42" s="3">
         <v>1862800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1824900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2489800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>3258200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2474000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2078400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>2177200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2078000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1136600</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N42" s="3">
-        <v>0</v>
+      <c r="N42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O42" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="P42" s="3">
         <v>500</v>
@@ -2681,8 +2770,8 @@
       <c r="Q42" s="3">
         <v>500</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>3</v>
+      <c r="R42" s="3">
+        <v>500</v>
       </c>
       <c r="S42" s="3" t="s">
         <v>3</v>
@@ -2693,62 +2782,65 @@
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V42" s="3">
-        <v>0</v>
+      <c r="V42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>101400</v>
+        <v>109600</v>
       </c>
       <c r="E43" s="3">
-        <v>126900</v>
+        <v>113400</v>
       </c>
       <c r="F43" s="3">
-        <v>51800</v>
+        <v>138600</v>
       </c>
       <c r="G43" s="3">
-        <v>23400</v>
+        <v>62900</v>
       </c>
       <c r="H43" s="3">
-        <v>20600</v>
+        <v>33900</v>
       </c>
       <c r="I43" s="3">
-        <v>2600</v>
+        <v>27100</v>
       </c>
       <c r="J43" s="3">
+        <v>8400</v>
+      </c>
+      <c r="K43" s="3">
         <v>19500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>27700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>27900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>600</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2758,62 +2850,65 @@
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V43" s="3">
-        <v>0</v>
+      <c r="V43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>506800</v>
+      </c>
+      <c r="E44" s="3">
         <v>509900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>565700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>696200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>799000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>849800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1017600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>834400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>685300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>553000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>333900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>127300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>61200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>28200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>6300</v>
       </c>
-      <c r="R44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2823,68 +2918,71 @@
       <c r="U44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V44" s="3">
-        <v>0</v>
+      <c r="V44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>173800</v>
+        <v>96400</v>
       </c>
       <c r="E45" s="3">
-        <v>147000</v>
+        <v>90200</v>
       </c>
       <c r="F45" s="3">
-        <v>149400</v>
+        <v>63200</v>
       </c>
       <c r="G45" s="3">
-        <v>146600</v>
+        <v>67000</v>
       </c>
       <c r="H45" s="3">
-        <v>137300</v>
+        <v>58100</v>
       </c>
       <c r="I45" s="3">
-        <v>121300</v>
+        <v>55800</v>
       </c>
       <c r="J45" s="3">
+        <v>51500</v>
+      </c>
+      <c r="K45" s="3">
         <v>145100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>126300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>118100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>137800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>113700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>100600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>67900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>51200</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S45" s="3">
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T45" s="3">
         <v>1100</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2894,106 +2992,112 @@
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4247000</v>
+      </c>
+      <c r="E46" s="3">
         <v>4001500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4834000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4757200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5391500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6256900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4119800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4912000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4156400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4966500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5864400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>6507000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4986800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>682400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>868600</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S46" s="3">
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T46" s="3">
         <v>5300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>200</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>601200</v>
+      </c>
+      <c r="E47" s="3">
         <v>739100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>688400</v>
       </c>
-      <c r="F47" s="3">
-        <v>461000</v>
-      </c>
       <c r="G47" s="3">
+        <v>542500</v>
+      </c>
+      <c r="H47" s="3">
         <v>479700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>288100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>441700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>530000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>513700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>278100</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3009,12 +3113,12 @@
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S47" s="3">
+      <c r="S47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T47" s="3">
         <v>2070200</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3024,56 +3128,59 @@
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3442700</v>
+      </c>
+      <c r="E48" s="3">
         <v>3278600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3189300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3032400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2894700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2698500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2536100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2381900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2166200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1813600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1494200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1344100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1109700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1014400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>899900</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3083,14 +3190,17 @@
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V48" s="3">
-        <v>0</v>
+      <c r="V48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3154,8 +3264,11 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3219,8 +3332,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3284,73 +3400,79 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>198300</v>
+      </c>
+      <c r="E52" s="3">
         <v>204000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>185400</v>
       </c>
-      <c r="F52" s="3">
-        <v>262200</v>
-      </c>
       <c r="G52" s="3">
+        <v>180700</v>
+      </c>
+      <c r="H52" s="3">
         <v>175300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>171600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>163300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>55300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>51500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>71200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>43200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>30600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>42700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>39300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>31300</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S52" s="3">
-        <v>0</v>
+      <c r="S52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T52" s="3">
+        <v>0</v>
+      </c>
+      <c r="U52" s="3">
         <v>200</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3414,73 +3536,79 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8489200</v>
+      </c>
+      <c r="E54" s="3">
         <v>8223300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8897000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8512700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8941200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>9415100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7260900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7879200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6887800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7129400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7401800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7881700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6139200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1736100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1799800</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S54" s="3">
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T54" s="3">
         <v>2075500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>400</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3504,8 +3632,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3529,64 +3658,65 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>139200</v>
+      </c>
+      <c r="E57" s="3">
         <v>113600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>101500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>108700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>104600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>140100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>145700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>229100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>79800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>129100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>66400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>41300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>8900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>14000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>9200</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S57" s="3">
-        <v>0</v>
+      <c r="S57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T57" s="3">
         <v>0</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
+      <c r="U57" s="3">
+        <v>0</v>
       </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
@@ -3594,251 +3724,263 @@
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>75300</v>
+        <v>88400</v>
       </c>
       <c r="E58" s="3">
-        <v>80100</v>
+        <v>105600</v>
       </c>
       <c r="F58" s="3">
-        <v>80700</v>
+        <v>110300</v>
       </c>
       <c r="G58" s="3">
-        <v>61500</v>
+        <v>109200</v>
       </c>
       <c r="H58" s="3">
-        <v>23500</v>
+        <v>86400</v>
       </c>
       <c r="I58" s="3">
-        <v>19800</v>
+        <v>42700</v>
       </c>
       <c r="J58" s="3">
+        <v>35600</v>
+      </c>
+      <c r="K58" s="3">
         <v>20200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>25500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>7100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>8900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>19500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>27900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>10800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2500</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T58" s="3">
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U58" s="3">
         <v>300</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>821900</v>
+        <v>649400</v>
       </c>
       <c r="E59" s="3">
-        <v>855200</v>
+        <v>527100</v>
       </c>
       <c r="F59" s="3">
-        <v>819000</v>
+        <v>596100</v>
       </c>
       <c r="G59" s="3">
-        <v>871800</v>
+        <v>569400</v>
       </c>
       <c r="H59" s="3">
-        <v>722000</v>
+        <v>639700</v>
       </c>
       <c r="I59" s="3">
-        <v>849400</v>
+        <v>498000</v>
       </c>
       <c r="J59" s="3">
+        <v>444800</v>
+      </c>
+      <c r="K59" s="3">
         <v>688300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>719800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>517900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>436600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>335300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>232600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>175000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>247300</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T59" s="3">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U59" s="3">
         <v>100</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1146100</v>
+      </c>
+      <c r="E60" s="3">
         <v>1010900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1036700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1008400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1037900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>885600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1015000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>937600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>825100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>654100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>511900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>396100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>269400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>199800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>259100</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S60" s="3">
-        <v>0</v>
+      <c r="S60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T60" s="3">
+        <v>0</v>
+      </c>
+      <c r="U60" s="3">
         <v>400</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2076100</v>
+        <v>2315900</v>
       </c>
       <c r="E61" s="3">
-        <v>2074100</v>
+        <v>2310400</v>
       </c>
       <c r="F61" s="3">
-        <v>2074600</v>
+        <v>2313100</v>
       </c>
       <c r="G61" s="3">
-        <v>2072700</v>
+        <v>2318700</v>
       </c>
       <c r="H61" s="3">
-        <v>2073500</v>
+        <v>2319500</v>
       </c>
       <c r="I61" s="3">
-        <v>2072000</v>
+        <v>2324100</v>
       </c>
       <c r="J61" s="3">
+        <v>2311500</v>
+      </c>
+      <c r="K61" s="3">
         <v>2073200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2069900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1994600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1994100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1992900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4200</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -3854,62 +3996,65 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>969100</v>
+        <v>1171400</v>
       </c>
       <c r="E62" s="3">
-        <v>1049600</v>
+        <v>624800</v>
       </c>
       <c r="F62" s="3">
-        <v>578000</v>
+        <v>702700</v>
       </c>
       <c r="G62" s="3">
-        <v>424700</v>
+        <v>226100</v>
       </c>
       <c r="H62" s="3">
-        <v>496100</v>
+        <v>177800</v>
       </c>
       <c r="I62" s="3">
-        <v>542200</v>
+        <v>245600</v>
       </c>
       <c r="J62" s="3">
+        <v>302600</v>
+      </c>
+      <c r="K62" s="3">
         <v>518800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>761500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>770400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1066300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1583400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1019900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>164800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1309500</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S62" s="3">
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T62" s="3">
         <v>72500</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3919,8 +4064,11 @@
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3984,8 +4132,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4049,8 +4200,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4114,73 +4268,79 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4745300</v>
+      </c>
+      <c r="E66" s="3">
         <v>4056100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4160400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3661000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3535200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3455200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3629100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3529500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3656600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3419000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3572400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3972400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1294000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>368500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1572800</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S66" s="3">
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T66" s="3">
         <v>72500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>400</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4204,8 +4364,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4269,8 +4430,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4334,20 +4498,23 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>1060200</v>
+      </c>
+      <c r="E70" s="3">
         <v>651300</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>504500</v>
       </c>
-      <c r="F70" s="3">
-        <v>0</v>
-      </c>
       <c r="G70" s="3">
         <v>0</v>
       </c>
@@ -4376,14 +4543,14 @@
         <v>0</v>
       </c>
       <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
         <v>5836800</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <v>4454800</v>
       </c>
-      <c r="R70" s="3">
-        <v>0</v>
-      </c>
       <c r="S70" s="3">
         <v>0</v>
       </c>
@@ -4399,8 +4566,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4464,64 +4634,67 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-12515500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-11523000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-10879600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-10198800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-9545000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-8914100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-8149900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-7370300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-6897700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-6367600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-6147200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-6065900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-5020200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-4495800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-4234100</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S72" s="3">
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T72" s="3">
         <v>-200</v>
       </c>
-      <c r="T72" s="3">
-        <v>0</v>
-      </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
+      <c r="U72" s="3">
+        <v>0</v>
       </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
@@ -4529,8 +4702,11 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4594,8 +4770,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4659,8 +4838,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4724,64 +4906,67 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2683700</v>
+      </c>
+      <c r="E76" s="3">
         <v>3515900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4232200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4851700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5406000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5959800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3631900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4349700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3231200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3710400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3829500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3909400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4845200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-4469200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-4227900</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S76" s="3">
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T76" s="3">
         <v>2003000</v>
       </c>
-      <c r="T76" s="3">
-        <v>0</v>
-      </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
+      <c r="U76" s="3">
+        <v>0</v>
       </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
@@ -4789,8 +4974,11 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4854,134 +5042,140 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-790300</v>
+        <v>-992500</v>
       </c>
       <c r="E81" s="3">
-        <v>-684800</v>
+        <v>-643400</v>
       </c>
       <c r="F81" s="3">
+        <v>-680900</v>
+      </c>
+      <c r="G81" s="3">
         <v>-653800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-630900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-764200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-779500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1726900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-530100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-220400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-81300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1045700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-524400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-261700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2915300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-297500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-200</v>
       </c>
-      <c r="T81" s="3">
-        <v>0</v>
-      </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
+      <c r="U81" s="3">
+        <v>0</v>
       </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
@@ -4989,8 +5183,11 @@
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5014,64 +5211,65 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>66200</v>
+        <v>60800</v>
       </c>
       <c r="E83" s="3">
-        <v>68800</v>
+        <v>55400</v>
       </c>
       <c r="F83" s="3">
-        <v>67500</v>
+        <v>49800</v>
       </c>
       <c r="G83" s="3">
-        <v>60800</v>
+        <v>55200</v>
       </c>
       <c r="H83" s="3">
-        <v>55400</v>
+        <v>50700</v>
       </c>
       <c r="I83" s="3">
-        <v>49800</v>
+        <v>42400</v>
       </c>
       <c r="J83" s="3">
+        <v>38200</v>
+      </c>
+      <c r="K83" s="3">
         <v>55200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>50700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>42400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>38200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>36300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>14900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>6800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>4800</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U83" s="3">
-        <v>0</v>
+      <c r="U83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V83" s="3">
         <v>0</v>
@@ -5079,8 +5277,11 @@
       <c r="W83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5144,8 +5345,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5209,8 +5413,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5274,8 +5481,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5339,8 +5549,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5404,64 +5617,67 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-462800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-507000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-516700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-474500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-513600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-700400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-801300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-648500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-569500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-513600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-494600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-312700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-291600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-235100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-218700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-192800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1400</v>
       </c>
-      <c r="T89" s="3">
-        <v>0</v>
-      </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
+      <c r="U89" s="3">
+        <v>0</v>
       </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
@@ -5469,8 +5685,11 @@
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5494,64 +5713,65 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-159700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-234300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-198200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-272600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-192500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-203700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-241800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-289900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-290100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-309800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-185100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-121900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-92800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-111800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-94800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-103700</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
+      <c r="U91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
@@ -5559,8 +5779,11 @@
       <c r="W91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5624,8 +5847,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5689,59 +5915,62 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>283700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-311300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>317500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>652200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1132400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-438000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-28700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-392700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1374900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1729000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-185100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-121400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-92800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-111700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-94800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-103700</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5754,8 +5983,11 @@
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5779,31 +6011,32 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5844,8 +6077,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5909,8 +6145,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5974,8 +6213,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6039,96 +6281,102 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>719100</v>
+      </c>
+      <c r="E100" s="3">
         <v>2400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>997200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>28000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>35100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>3013600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-5700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1512800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>17600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>4100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-187300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1899600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>4624700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>101000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>511100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>398000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2075400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>200</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -6169,69 +6417,75 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>540100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-815900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>798000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>205600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1610900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1875300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-835700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>471600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1926700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2238600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-867000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1465500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>4240400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-245800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>197600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>101500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>4000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>200</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LCID_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LCID_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="92">
   <si>
     <t>LCID</t>
   </si>
@@ -656,229 +656,235 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="8" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>234500</v>
+      </c>
+      <c r="E8" s="3">
         <v>200000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>200600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>172700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>157200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>137800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>150900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>149400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>257700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>195500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>97300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>57700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>26400</v>
-      </c>
-      <c r="P8" s="3">
-        <v>200</v>
       </c>
       <c r="Q8" s="3">
         <v>200</v>
       </c>
       <c r="R8" s="3">
+        <v>200</v>
+      </c>
+      <c r="S8" s="3">
         <v>300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3600</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W8" s="3">
-        <v>0</v>
+      <c r="W8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>443200</v>
+      </c>
+      <c r="E9" s="3">
         <v>412500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>470400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>404800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>410000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>469700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>555800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>500500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>615300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>492500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>292300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>246000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>151500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3300</v>
       </c>
-      <c r="Q9" s="3">
-        <v>0</v>
-      </c>
       <c r="R9" s="3">
+        <v>0</v>
+      </c>
+      <c r="S9" s="3">
         <v>100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2500</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
@@ -891,62 +897,65 @@
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-208800</v>
+      </c>
+      <c r="E10" s="3">
         <v>-212500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-269800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-232100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-252900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-331900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-404900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-351100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-357600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-297000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-195000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-188300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-125100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-3100</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>200</v>
       </c>
       <c r="R10" s="3">
         <v>200</v>
       </c>
       <c r="S10" s="3">
+        <v>200</v>
+      </c>
+      <c r="T10" s="3">
         <v>1100</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
@@ -959,8 +968,11 @@
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -985,62 +997,63 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>280300</v>
+      </c>
+      <c r="E12" s="3">
         <v>324400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>287200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>284600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>243000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>230800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>233500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>229800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>221300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>213800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>200400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>186100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>163600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>242400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>176800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>167400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>169500</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1053,8 +1066,11 @@
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1121,53 +1137,56 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E14" s="3">
         <v>8900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>29600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>19900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-6000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>22500</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>2700</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1183,41 +1202,44 @@
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>90800</v>
+      </c>
+      <c r="E15" s="3">
         <v>69500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>66200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>68800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>67500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>60800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>55400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>49800</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1257,8 +1279,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1280,67 +1305,68 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>967400</v>
+      </c>
+      <c r="E17" s="3">
         <v>970500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>967800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>902700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>894000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>890200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>987000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>899100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1007500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>883000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>656500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>655200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>512100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>500000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>249100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>299100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>203300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>300</v>
       </c>
-      <c r="U17" s="3">
-        <v>0</v>
-      </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
+      <c r="V17" s="3">
+        <v>0</v>
       </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
@@ -1348,62 +1374,65 @@
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-733000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-770500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-767200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-729900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-736900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-752400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-836200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-749700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-749800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-687500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-559200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-597500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-485700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-499800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-248900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-298800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-199700</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1416,8 +1445,11 @@
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1442,62 +1474,63 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-293700</v>
+      </c>
+      <c r="E20" s="3">
         <v>254200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-105500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-26000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-26200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-59600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-41200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>40100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>285000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>158400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>339000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>516700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-559900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-24500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-12700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-449100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-111400</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1510,62 +1543,65 @@
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-348400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-955100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-595500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-635000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-643200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-632000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-739600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-740000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-409500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-478400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-177800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-42600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1009200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-509400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-254800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-743000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-306400</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1578,40 +1614,43 @@
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E22" s="3">
         <v>8500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>6700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>7500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>7800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>3300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>6700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>7100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>8100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>900</v>
-      </c>
-      <c r="M22" s="3">
-        <v>100</v>
       </c>
       <c r="N22" s="3">
         <v>100</v>
@@ -1629,10 +1668,10 @@
         <v>100</v>
       </c>
       <c r="S22" s="3">
-        <v>0</v>
-      </c>
-      <c r="T22" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="T22" s="3">
+        <v>0</v>
       </c>
       <c r="U22" s="3" t="s">
         <v>3</v>
@@ -1646,67 +1685,70 @@
       <c r="X22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-396600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-992000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-643500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-680700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-653800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-630600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-763600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-779400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-472800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-530000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-220400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-81000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1045700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-524400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-261700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-747900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-311200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-200</v>
       </c>
-      <c r="U23" s="3">
-        <v>0</v>
-      </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
+      <c r="V23" s="3">
+        <v>0</v>
       </c>
       <c r="W23" s="3" t="s">
         <v>3</v>
@@ -1714,47 +1756,50 @@
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>600</v>
+      </c>
+      <c r="E24" s="3">
         <v>500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>200</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-200</v>
-      </c>
-      <c r="L24" s="3">
-        <v>100</v>
       </c>
       <c r="M24" s="3">
         <v>100</v>
       </c>
       <c r="N24" s="3">
+        <v>100</v>
+      </c>
+      <c r="O24" s="3">
         <v>300</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
         <v>0</v>
       </c>
@@ -1765,16 +1810,16 @@
         <v>0</v>
       </c>
       <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>100</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
       <c r="U24" s="3">
         <v>0</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>3</v>
+      <c r="V24" s="3">
+        <v>0</v>
       </c>
       <c r="W24" s="3" t="s">
         <v>3</v>
@@ -1782,8 +1827,11 @@
       <c r="X24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1850,67 +1898,70 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-397200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-992500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-643400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-680900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-653800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-630900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-764200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-779500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-472600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-530100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-220400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-81300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1045700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-524400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-261700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-748000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-311300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-200</v>
       </c>
-      <c r="U26" s="3">
-        <v>0</v>
-      </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
+      <c r="V26" s="3">
+        <v>0</v>
       </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
@@ -1918,67 +1969,70 @@
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-636900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-949600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-790300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-684800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-653800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-630900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-764200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-779500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1726900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-530100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-220400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-81300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1045700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-524400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-261700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2915300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-297500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-200</v>
       </c>
-      <c r="U27" s="3">
-        <v>0</v>
-      </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
+      <c r="V27" s="3">
+        <v>0</v>
       </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
@@ -1986,8 +2040,11 @@
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2054,8 +2111,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2122,8 +2182,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2190,8 +2253,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2258,62 +2324,65 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>293700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-254200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>105500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>26000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>26200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>59600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>41200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-40100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-285000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-158400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-339000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-516700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>559900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>24500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>12700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>449100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>111400</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2326,67 +2395,70 @@
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-397200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-992500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-643400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-680900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-653800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-630900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-764200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-779500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1726900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-530100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-220400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-81300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1045700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-524400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-261700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2915300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-297500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-200</v>
       </c>
-      <c r="U33" s="3">
-        <v>0</v>
-      </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
+      <c r="V33" s="3">
+        <v>0</v>
       </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
@@ -2394,8 +2466,11 @@
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2462,67 +2537,70 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-397200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-992500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-643400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-680900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-653800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-630900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-764200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-779500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1726900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-530100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-220400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-81300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1045700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-524400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-261700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2915300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-297500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-200</v>
       </c>
-      <c r="U35" s="3">
-        <v>0</v>
-      </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
+      <c r="V35" s="3">
+        <v>0</v>
       </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
@@ -2530,81 +2608,87 @@
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2629,8 +2713,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2655,117 +2740,121 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1606900</v>
+      </c>
+      <c r="E41" s="3">
         <v>1893600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1353600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2169500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1369900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1164400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2775300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>900000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1735800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1264100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3157400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5391800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>6262900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4796900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>557900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>810000</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T41" s="3">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U41" s="3">
         <v>4200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>200</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2424100</v>
+      </c>
+      <c r="E42" s="3">
         <v>1578300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1862800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1824900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2489800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>3258200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2474000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>2078400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2177200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2078000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1136600</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O42" s="3">
-        <v>0</v>
+      <c r="O42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P42" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="Q42" s="3">
         <v>500</v>
@@ -2773,8 +2862,8 @@
       <c r="R42" s="3">
         <v>500</v>
       </c>
-      <c r="S42" s="3" t="s">
-        <v>3</v>
+      <c r="S42" s="3">
+        <v>500</v>
       </c>
       <c r="T42" s="3" t="s">
         <v>3</v>
@@ -2785,65 +2874,68 @@
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W42" s="3">
-        <v>0</v>
+      <c r="W42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>131600</v>
+      </c>
+      <c r="E43" s="3">
         <v>109600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>113400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>138600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>62900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>33900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>27100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>8400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>19500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>27700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>27900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>600</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2853,65 +2945,68 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W43" s="3">
-        <v>0</v>
+      <c r="W43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>407800</v>
+      </c>
+      <c r="E44" s="3">
         <v>506800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>509900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>565700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>696200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>799000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>849800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1017600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>834400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>685300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>553000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>333900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>127300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>61200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>28200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>6300</v>
       </c>
-      <c r="S44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2921,71 +3016,74 @@
       <c r="V44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W44" s="3">
-        <v>0</v>
+      <c r="W44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>250600</v>
+      </c>
+      <c r="E45" s="3">
         <v>96400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>90200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>63200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>67000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>58100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>55800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>51500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>145100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>126300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>118100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>137800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>113700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>100600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>67900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>51200</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T45" s="3">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U45" s="3">
         <v>1100</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2995,112 +3093,118 @@
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4873900</v>
+      </c>
+      <c r="E46" s="3">
         <v>4247000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4001500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4834000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4757200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5391500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6256900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4119800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4912000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4156400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4966500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5864400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>6507000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4986800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>682400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>868600</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T46" s="3">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U46" s="3">
         <v>5300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>200</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1050100</v>
+      </c>
+      <c r="E47" s="3">
         <v>601200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>739100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>688400</v>
       </c>
-      <c r="G47" s="3">
-        <v>542500</v>
-      </c>
       <c r="H47" s="3">
+        <v>542600</v>
+      </c>
+      <c r="I47" s="3">
         <v>479700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>288100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>441700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>530000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>513700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>278100</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3116,12 +3220,12 @@
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T47" s="3">
+      <c r="T47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U47" s="3">
         <v>2070200</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3131,59 +3235,62 @@
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3474500</v>
+      </c>
+      <c r="E48" s="3">
         <v>3442700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3278600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3189300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3032400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2894700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2698500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2536100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2381900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2166200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1813600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1494200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1344100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1109700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1014400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>899900</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3193,14 +3300,17 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W48" s="3">
-        <v>0</v>
+      <c r="W48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3267,8 +3377,11 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3335,8 +3448,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3403,76 +3519,82 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>249400</v>
+      </c>
+      <c r="E52" s="3">
         <v>198300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>204000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>185400</v>
       </c>
-      <c r="G52" s="3">
-        <v>180700</v>
-      </c>
       <c r="H52" s="3">
+        <v>180600</v>
+      </c>
+      <c r="I52" s="3">
         <v>175300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>171600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>163300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>55300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>51500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>71200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>43200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>30600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>42700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>39300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>31300</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T52" s="3">
-        <v>0</v>
+      <c r="T52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U52" s="3">
+        <v>0</v>
+      </c>
+      <c r="V52" s="3">
         <v>200</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3539,76 +3661,82 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>9647900</v>
+      </c>
+      <c r="E54" s="3">
         <v>8489200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8223300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8897000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8512700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8941200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>9415100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7260900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7879200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6887800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7129400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7401800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7881700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6139200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1736100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1799800</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T54" s="3">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U54" s="3">
         <v>2075500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>400</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3633,8 +3761,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3659,67 +3788,68 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>133800</v>
+      </c>
+      <c r="E57" s="3">
         <v>139200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>113600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>101500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>108700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>104600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>140100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>145700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>229100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>79800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>129100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>66400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>41300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>8900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>14000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>9200</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T57" s="3">
-        <v>0</v>
+      <c r="T57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U57" s="3">
         <v>0</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
+      <c r="V57" s="3">
+        <v>0</v>
       </c>
       <c r="W57" s="3" t="s">
         <v>3</v>
@@ -3727,263 +3857,275 @@
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>168800</v>
+      </c>
+      <c r="E58" s="3">
         <v>88400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>105600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>110300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>109200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>86400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>42700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>35600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>20200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>25500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>7100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>8900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>19500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>27900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>10800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2500</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U58" s="3">
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V58" s="3">
         <v>300</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>549400</v>
+      </c>
+      <c r="E59" s="3">
         <v>649400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>527100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>596100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>569400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>639700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>498000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>444800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>688300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>719800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>517900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>436600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>335300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>232600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>175000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>247300</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U59" s="3">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V59" s="3">
         <v>100</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1165300</v>
+      </c>
+      <c r="E60" s="3">
         <v>1146100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1010900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1036700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1008400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1037900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>885600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1015000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>937600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>825100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>654100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>511900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>396100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>269400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>199800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>259100</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T60" s="3">
-        <v>0</v>
+      <c r="T60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U60" s="3">
+        <v>0</v>
+      </c>
+      <c r="V60" s="3">
         <v>400</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2308100</v>
+      </c>
+      <c r="E61" s="3">
         <v>2315900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2310400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2313100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2318700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2319500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2324100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2311500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2073200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2069900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1994600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1994100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1992900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>4200</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -3999,65 +4141,68 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>889200</v>
+      </c>
+      <c r="E62" s="3">
         <v>1171400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>624800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>702700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>226100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>177800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>245600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>302600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>518800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>761500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>770400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1066300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1583400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1019900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>164800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1309500</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T62" s="3">
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U62" s="3">
         <v>72500</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4067,8 +4212,11 @@
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4135,8 +4283,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4203,8 +4354,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4271,76 +4425,82 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4475300</v>
+      </c>
+      <c r="E66" s="3">
         <v>4745300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4056100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4160400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3661000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3535200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3455200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3629100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3529500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3656600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3419000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3572400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3972400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1294000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>368500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1572800</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T66" s="3">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U66" s="3">
         <v>72500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>400</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4365,8 +4525,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4433,8 +4594,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4501,23 +4665,26 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>1299800</v>
+      </c>
+      <c r="E70" s="3">
         <v>1060200</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>651300</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>504500</v>
       </c>
-      <c r="G70" s="3">
-        <v>0</v>
-      </c>
       <c r="H70" s="3">
         <v>0</v>
       </c>
@@ -4546,14 +4713,14 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
         <v>5836800</v>
       </c>
-      <c r="R70" s="3">
+      <c r="S70" s="3">
         <v>4454800</v>
       </c>
-      <c r="S70" s="3">
-        <v>0</v>
-      </c>
       <c r="T70" s="3">
         <v>0</v>
       </c>
@@ -4569,8 +4736,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4637,67 +4807,70 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-12912700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-12515500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-11523000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-10879600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-10198800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-9545000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-8914100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-8149900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-7370300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-6897700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-6367600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-6147200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-6065900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-5020200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-4495800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-4234100</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T72" s="3">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U72" s="3">
         <v>-200</v>
       </c>
-      <c r="U72" s="3">
-        <v>0</v>
-      </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
+      <c r="V72" s="3">
+        <v>0</v>
       </c>
       <c r="W72" s="3" t="s">
         <v>3</v>
@@ -4705,8 +4878,11 @@
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4773,8 +4949,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4841,8 +5020,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4909,67 +5091,70 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3872800</v>
+      </c>
+      <c r="E76" s="3">
         <v>2683700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3515900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4232200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4851700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5406000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5959800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3631900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4349700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3231200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3710400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3829500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3909400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4845200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-4469200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-4227900</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T76" s="3">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U76" s="3">
         <v>2003000</v>
       </c>
-      <c r="U76" s="3">
-        <v>0</v>
-      </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
+      <c r="V76" s="3">
+        <v>0</v>
       </c>
       <c r="W76" s="3" t="s">
         <v>3</v>
@@ -4977,8 +5162,11 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5045,140 +5233,146 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-397200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-992500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-643400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-680900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-653800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-630900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-764200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-779500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1726900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-530100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-220400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-81300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1045700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-524400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-261700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2915300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-297500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-200</v>
       </c>
-      <c r="U81" s="3">
-        <v>0</v>
-      </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
+      <c r="V81" s="3">
+        <v>0</v>
       </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
@@ -5186,8 +5380,11 @@
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5212,67 +5409,68 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>67500</v>
+      </c>
+      <c r="E83" s="3">
         <v>60800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>55400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>49800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>55200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>50700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>42400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>38200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>55200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>50700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>42400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>38200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>36300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>14900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>6800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>4900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>4800</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V83" s="3">
-        <v>0</v>
+      <c r="V83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W83" s="3">
         <v>0</v>
@@ -5280,8 +5478,11 @@
       <c r="X83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5348,8 +5549,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5416,8 +5620,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5484,8 +5691,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5552,8 +5762,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5620,67 +5833,70 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-533100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-462800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-507000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-516700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-474500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-513600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-700400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-801300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-648500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-569500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-513600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-494600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-312700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-291600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-235100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-218700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-192800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-1400</v>
       </c>
-      <c r="U89" s="3">
-        <v>0</v>
-      </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
+      <c r="V89" s="3">
+        <v>0</v>
       </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
@@ -5688,8 +5904,11 @@
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5714,67 +5933,68 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-291600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-159700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-234300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-198200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-272600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-192500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-203700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-241800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-289900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-290100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-309800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-185100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-121900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-92800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-111800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-94800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-103700</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
+      <c r="V91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W91" s="3">
         <v>0</v>
@@ -5782,8 +6002,11 @@
       <c r="X91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5850,8 +6073,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5918,62 +6144,65 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1584400</v>
+      </c>
+      <c r="E94" s="3">
         <v>283700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-311300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>317500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>652200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1132400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-438000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-28700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-392700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1374900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1729000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-185100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-121400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-92800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-111700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-94800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-103700</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5986,8 +6215,11 @@
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6012,8 +6244,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6038,8 +6271,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -6080,8 +6313,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6148,8 +6384,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6216,8 +6455,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6284,76 +6526,82 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1831000</v>
+      </c>
+      <c r="E100" s="3">
         <v>719100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>997200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>28000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>35100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>3013600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-5700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1512800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>17600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>4100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-187300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1899600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>4624700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>101000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>511100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>398000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>2075400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>200</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6378,8 +6626,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -6420,72 +6668,78 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-286600</v>
+      </c>
+      <c r="E102" s="3">
         <v>540100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-815900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>798000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>205600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1610900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1875300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-835700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>471600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1926700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2238600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-867000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1465500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>4240400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-245800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>197600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>101500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>4000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>200</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LCID_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LCID_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="92">
   <si>
     <t>LCID</t>
   </si>
@@ -656,238 +656,244 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="9" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>235000</v>
+      </c>
+      <c r="E8" s="3">
         <v>234500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>200000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>200600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>172700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>157200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>137800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>150900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>149400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>257700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>195500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>97300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>57700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>26400</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>200</v>
       </c>
       <c r="R8" s="3">
         <v>200</v>
       </c>
       <c r="S8" s="3">
+        <v>200</v>
+      </c>
+      <c r="T8" s="3">
         <v>300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3600</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X8" s="3">
-        <v>0</v>
+      <c r="X8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>463600</v>
+      </c>
+      <c r="E9" s="3">
         <v>443200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>412500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>470400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>404800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>410000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>469700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>555800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>500500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>615300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>492500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>292300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>246000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>151500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3300</v>
       </c>
-      <c r="R9" s="3">
-        <v>0</v>
-      </c>
       <c r="S9" s="3">
+        <v>0</v>
+      </c>
+      <c r="T9" s="3">
         <v>100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2500</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
@@ -900,65 +906,68 @@
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-228500</v>
+      </c>
+      <c r="E10" s="3">
         <v>-208800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-212500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-269800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-232100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-252900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-331900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-404900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-351100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-357600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-297000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-195000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-188300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-125100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-3100</v>
-      </c>
-      <c r="R10" s="3">
-        <v>200</v>
       </c>
       <c r="S10" s="3">
         <v>200</v>
       </c>
       <c r="T10" s="3">
+        <v>200</v>
+      </c>
+      <c r="U10" s="3">
         <v>1100</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
@@ -971,8 +980,11 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -998,65 +1010,66 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>251200</v>
+      </c>
+      <c r="E12" s="3">
         <v>280300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>324400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>287200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>284600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>243000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>230800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>233500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>229800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>221300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>213800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>200400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>186100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>163600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>242400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>176800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>167400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>169500</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1069,8 +1082,11 @@
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1140,56 +1156,59 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E14" s="3">
         <v>4900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>8900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>29600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>19900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-6000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>22500</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>2700</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1205,44 +1224,47 @@
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>98000</v>
+      </c>
+      <c r="E15" s="3">
         <v>90800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>69500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>66200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>68800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>67500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>60800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>55400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>49800</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1282,8 +1304,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1306,70 +1331,71 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>927000</v>
+      </c>
+      <c r="E17" s="3">
         <v>967400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>970500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>967800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>902700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>894000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>890200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>987000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>899100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1007500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>883000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>656500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>655200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>512100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>500000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>249100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>299100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>203300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>300</v>
       </c>
-      <c r="V17" s="3">
-        <v>0</v>
-      </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
+      <c r="W17" s="3">
+        <v>0</v>
       </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
@@ -1377,65 +1403,68 @@
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-691900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-733000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-770500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-767200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-729900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-736900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-752400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-836200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-749700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-749800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-687500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-559200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-597500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-485700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-499800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-248900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-298800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-199700</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1448,8 +1477,11 @@
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1475,65 +1507,66 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-297500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-293700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>254200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-105500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-26000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-26200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-59600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-41200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>40100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>285000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>158400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>339000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>516700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-559900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-24500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-12700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-449100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-111400</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1546,65 +1579,68 @@
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-296400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-348400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-955100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-595500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-635000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-643200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-632000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-739600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-740000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-409500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-478400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-177800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-42600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-1009200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-509400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-254800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-743000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-306400</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1617,43 +1653,46 @@
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E22" s="3">
         <v>10300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>8500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>6700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>7500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>7800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>3300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>6700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>7100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>8100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>900</v>
-      </c>
-      <c r="N22" s="3">
-        <v>100</v>
       </c>
       <c r="O22" s="3">
         <v>100</v>
@@ -1671,10 +1710,10 @@
         <v>100</v>
       </c>
       <c r="T22" s="3">
-        <v>0</v>
-      </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="U22" s="3">
+        <v>0</v>
       </c>
       <c r="V22" s="3" t="s">
         <v>3</v>
@@ -1688,70 +1727,73 @@
       <c r="Y22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-367500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-396600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-992000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-643500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-680700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-653800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-630600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-763600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-779400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-472800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-530000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-220400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-81000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1045700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-524400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-261700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-747900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-311200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-200</v>
       </c>
-      <c r="V23" s="3">
-        <v>0</v>
-      </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
+      <c r="W23" s="3">
+        <v>0</v>
       </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
@@ -1759,50 +1801,53 @@
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E24" s="3">
         <v>600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>200</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-200</v>
-      </c>
-      <c r="M24" s="3">
-        <v>100</v>
       </c>
       <c r="N24" s="3">
         <v>100</v>
       </c>
       <c r="O24" s="3">
+        <v>100</v>
+      </c>
+      <c r="P24" s="3">
         <v>300</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
         <v>0</v>
       </c>
@@ -1813,16 +1858,16 @@
         <v>0</v>
       </c>
       <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>100</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
       <c r="V24" s="3">
         <v>0</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>3</v>
+      <c r="W24" s="3">
+        <v>0</v>
       </c>
       <c r="X24" s="3" t="s">
         <v>3</v>
@@ -1830,8 +1875,11 @@
       <c r="Y24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1901,70 +1949,73 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-366200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-397200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-992500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-643400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-680900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-653800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-630900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-764200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-779500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-472600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-530100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-220400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-81300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1045700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-524400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-261700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-748000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-311300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-200</v>
       </c>
-      <c r="V26" s="3">
-        <v>0</v>
-      </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
+      <c r="W26" s="3">
+        <v>0</v>
       </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
@@ -1972,70 +2023,73 @@
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-731100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-636900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-949600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-790300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-684800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-653800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-630900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-764200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-779500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1726900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-530100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-220400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-81300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1045700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-524400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-261700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2915300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-297500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-200</v>
       </c>
-      <c r="V27" s="3">
-        <v>0</v>
-      </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
+      <c r="W27" s="3">
+        <v>0</v>
       </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
@@ -2043,8 +2097,11 @@
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2114,8 +2171,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2185,8 +2245,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2256,8 +2319,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2327,65 +2393,68 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>297500</v>
+      </c>
+      <c r="E32" s="3">
         <v>293700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-254200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>105500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>26000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>26200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>59600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>41200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-40100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-285000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-158400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-339000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-516700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>559900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>24500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>12700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>449100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>111400</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2398,70 +2467,73 @@
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-366200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-397200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-992500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-643400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-680900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-653800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-630900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-764200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-779500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1726900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-530100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-220400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-81300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1045700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-524400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-261700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2915300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-297500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-200</v>
       </c>
-      <c r="V33" s="3">
-        <v>0</v>
-      </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
+      <c r="W33" s="3">
+        <v>0</v>
       </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
@@ -2469,8 +2541,11 @@
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2540,70 +2615,73 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-366200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-397200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-992500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-643400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-680900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-653800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-630900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-764200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-779500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1726900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-530100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-220400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-81300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1045700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-524400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-261700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2915300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-297500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-200</v>
       </c>
-      <c r="V35" s="3">
-        <v>0</v>
-      </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
+      <c r="W35" s="3">
+        <v>0</v>
       </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
@@ -2611,84 +2689,90 @@
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2714,8 +2798,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2741,123 +2826,127 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1854900</v>
+      </c>
+      <c r="E41" s="3">
         <v>1606900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1893600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1353600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2169500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1369900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1164400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2775300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>900000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1735800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1264100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3157400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5391800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>6262900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4796900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>557900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>810000</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U41" s="3">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V41" s="3">
         <v>4200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>200</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1756000</v>
+      </c>
+      <c r="E42" s="3">
         <v>2424100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1578300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1862800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1824900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2489800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>3258200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>2474000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2078400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2177200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2078000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1136600</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P42" s="3">
-        <v>0</v>
+      <c r="P42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q42" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="R42" s="3">
         <v>500</v>
@@ -2865,8 +2954,8 @@
       <c r="S42" s="3">
         <v>500</v>
       </c>
-      <c r="T42" s="3" t="s">
-        <v>3</v>
+      <c r="T42" s="3">
+        <v>500</v>
       </c>
       <c r="U42" s="3" t="s">
         <v>3</v>
@@ -2877,68 +2966,71 @@
       <c r="W42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X42" s="3">
-        <v>0</v>
+      <c r="X42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>114600</v>
+      </c>
+      <c r="E43" s="3">
         <v>131600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>109600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>113400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>138600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>62900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>33900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>27100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>8400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>19500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>27700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>27900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>600</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2948,68 +3040,71 @@
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X43" s="3">
-        <v>0</v>
+      <c r="X43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>471400</v>
+      </c>
+      <c r="E44" s="3">
         <v>407800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>506800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>509900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>565700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>696200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>799000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>849800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1017600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>834400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>685300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>553000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>333900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>127300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>61200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>28200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>6300</v>
       </c>
-      <c r="T44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3019,74 +3114,77 @@
       <c r="W44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X44" s="3">
-        <v>0</v>
+      <c r="X44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>174800</v>
+      </c>
+      <c r="E45" s="3">
         <v>250600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>96400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>90200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>63200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>67000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>58100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>55800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>51500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>145100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>126300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>118100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>137800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>113700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>100600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>67900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>51200</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U45" s="3">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V45" s="3">
         <v>1100</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3096,118 +3194,124 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4423300</v>
+      </c>
+      <c r="E46" s="3">
         <v>4873900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4247000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4001500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4834000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4757200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5391500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6256900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4119800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4912000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4156400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4966500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5864400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>6507000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>4986800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>682400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>868600</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U46" s="3">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V46" s="3">
         <v>5300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>200</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>947200</v>
+      </c>
+      <c r="E47" s="3">
         <v>1050100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>601200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>739100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>688400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>542600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>479700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>288100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>441700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>530000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>513700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>278100</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3223,12 +3327,12 @@
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U47" s="3">
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V47" s="3">
         <v>2070200</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3238,62 +3342,65 @@
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3553100</v>
+      </c>
+      <c r="E48" s="3">
         <v>3474500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3442700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3278600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3189300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3032400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2894700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2698500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2536100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2381900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2166200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1813600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1494200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1344100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1109700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1014400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>899900</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3303,14 +3410,17 @@
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X48" s="3">
-        <v>0</v>
+      <c r="X48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3380,8 +3490,11 @@
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3451,8 +3564,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3522,79 +3638,85 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>294500</v>
+      </c>
+      <c r="E52" s="3">
         <v>249400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>198300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>204000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>185400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>180600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>175300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>171600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>163300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>55300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>51500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>71200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>43200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>30600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>42700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>39300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>31300</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U52" s="3">
-        <v>0</v>
+      <c r="U52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V52" s="3">
+        <v>0</v>
+      </c>
+      <c r="W52" s="3">
         <v>200</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3664,79 +3786,85 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>9218000</v>
+      </c>
+      <c r="E54" s="3">
         <v>9647900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8489200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8223300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8897000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8512700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8941200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>9415100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7260900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7879200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6887800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7129400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7401800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7881700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6139200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1736100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1799800</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U54" s="3">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V54" s="3">
         <v>2075500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>400</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3762,8 +3890,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3789,70 +3918,71 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>121300</v>
+      </c>
+      <c r="E57" s="3">
         <v>133800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>139200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>113600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>101500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>108700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>104600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>140100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>145700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>229100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>79800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>129100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>66400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>41300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>8900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>14000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>9200</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U57" s="3">
-        <v>0</v>
+      <c r="U57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V57" s="3">
         <v>0</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
+      <c r="W57" s="3">
+        <v>0</v>
       </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
@@ -3860,275 +3990,287 @@
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>242500</v>
+      </c>
+      <c r="E58" s="3">
         <v>168800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>88400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>105600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>110300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>109200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>86400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>42700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>35600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>20200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>25500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>7100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>8900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>19500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>27900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>10800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2500</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V58" s="3">
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W58" s="3">
         <v>300</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>556800</v>
+      </c>
+      <c r="E59" s="3">
         <v>549400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>649400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>527100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>596100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>569400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>639700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>498000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>444800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>688300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>719800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>517900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>436600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>335300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>232600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>175000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>247300</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V59" s="3">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W59" s="3">
         <v>100</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1331500</v>
+      </c>
+      <c r="E60" s="3">
         <v>1165300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1146100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1010900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1036700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1008400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1037900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>885600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1015000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>937600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>825100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>654100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>511900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>396100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>269400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>199800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>259100</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U60" s="3">
-        <v>0</v>
+      <c r="U60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V60" s="3">
+        <v>0</v>
+      </c>
+      <c r="W60" s="3">
         <v>400</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2315700</v>
+      </c>
+      <c r="E61" s="3">
         <v>2308100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2315900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2310400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2313100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2318700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2319500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2324100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2311500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2073200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2069900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1994600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1994100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1992900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>4000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4200</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -4144,68 +4286,71 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>609000</v>
+      </c>
+      <c r="E62" s="3">
         <v>889200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1171400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>624800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>702700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>226100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>177800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>245600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>302600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>518800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>761500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>770400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1066300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1583400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1019900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>164800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1309500</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U62" s="3">
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V62" s="3">
         <v>72500</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4215,8 +4360,11 @@
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4286,8 +4434,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4357,8 +4508,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4428,79 +4582,85 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4369500</v>
+      </c>
+      <c r="E66" s="3">
         <v>4475300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4745300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4056100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4160400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3661000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3535200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3455200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3629100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3529500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3656600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3419000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3572400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3972400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1294000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>368500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1572800</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U66" s="3">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V66" s="3">
         <v>72500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>400</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4526,8 +4686,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4597,8 +4758,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4668,26 +4832,29 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>1664800</v>
+      </c>
+      <c r="E70" s="3">
         <v>1299800</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>1060200</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>651300</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>504500</v>
       </c>
-      <c r="H70" s="3">
-        <v>0</v>
-      </c>
       <c r="I70" s="3">
         <v>0</v>
       </c>
@@ -4716,14 +4883,14 @@
         <v>0</v>
       </c>
       <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
         <v>5836800</v>
       </c>
-      <c r="S70" s="3">
+      <c r="T70" s="3">
         <v>4454800</v>
       </c>
-      <c r="T70" s="3">
-        <v>0</v>
-      </c>
       <c r="U70" s="3">
         <v>0</v>
       </c>
@@ -4739,8 +4906,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4810,70 +4980,73 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-13278900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-12912700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-12515500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-11523000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-10879600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-10198800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-9545000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-8914100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-8149900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-7370300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-6897700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-6367600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-6147200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-6065900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-5020200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-4495800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-4234100</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U72" s="3">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V72" s="3">
         <v>-200</v>
       </c>
-      <c r="V72" s="3">
-        <v>0</v>
-      </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
+      <c r="W72" s="3">
+        <v>0</v>
       </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
@@ -4881,8 +5054,11 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4952,8 +5128,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5023,8 +5202,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5094,70 +5276,73 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3183700</v>
+      </c>
+      <c r="E76" s="3">
         <v>3872800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2683700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3515900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4232200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4851700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5406000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5959800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3631900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4349700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3231200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3710400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3829500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3909400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4845200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-4469200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-4227900</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U76" s="3">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V76" s="3">
         <v>2003000</v>
       </c>
-      <c r="V76" s="3">
-        <v>0</v>
-      </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
+      <c r="W76" s="3">
+        <v>0</v>
       </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
@@ -5165,8 +5350,11 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5236,146 +5424,152 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-366200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-397200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-992500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-643400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-680900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-653800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-630900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-764200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-779500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1726900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-530100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-220400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-81300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1045700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-524400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-261700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2915300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-297500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-200</v>
       </c>
-      <c r="V81" s="3">
-        <v>0</v>
-      </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
+      <c r="W81" s="3">
+        <v>0</v>
       </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
@@ -5383,8 +5577,11 @@
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5410,70 +5607,71 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>68800</v>
+      </c>
+      <c r="E83" s="3">
         <v>67500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>60800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>55400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>49800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>55200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>50700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>42400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>38200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>55200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>50700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>42400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>38200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>36300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>14900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>6800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>4900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>4800</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W83" s="3">
-        <v>0</v>
+      <c r="W83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X83" s="3">
         <v>0</v>
@@ -5481,8 +5679,11 @@
       <c r="Y83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5552,8 +5753,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5623,8 +5827,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5694,8 +5901,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5765,8 +5975,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5836,70 +6049,73 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-428600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-533100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-462800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-507000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-516700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-474500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-513600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-700400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-801300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-648500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-569500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-513600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-494600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-312700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-291600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-235100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-218700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-192800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-1400</v>
       </c>
-      <c r="V89" s="3">
-        <v>0</v>
-      </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
+      <c r="W89" s="3">
+        <v>0</v>
       </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
@@ -5907,8 +6123,11 @@
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5934,70 +6153,71 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-161200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-291600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-159700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-234300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-198200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-272600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-192500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-203700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-241800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-289900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-290100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-309800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-185100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-121900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-92800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-111800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-94800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-103700</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
+      <c r="W91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X91" s="3">
         <v>0</v>
@@ -6005,8 +6225,11 @@
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6076,8 +6299,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6147,65 +6373,68 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>614000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1584400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>283700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-311300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>317500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>652200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1132400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-438000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-28700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-392700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1374900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1729000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-185100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-121400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-92800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-111700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-94800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-103700</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6218,8 +6447,11 @@
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6245,8 +6477,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6274,8 +6507,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -6316,8 +6549,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6387,8 +6623,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6458,8 +6697,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6529,79 +6771,85 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>62700</v>
+      </c>
+      <c r="E100" s="3">
         <v>1831000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>719100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>997200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>28000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>35100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>3013600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-5700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1512800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>17600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>4100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-187300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1899600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>4624700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>101000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>511100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>398000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2075400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>200</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6629,8 +6877,8 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -6671,75 +6919,81 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>248100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-286600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>540100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-815900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>798000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>205600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1610900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1875300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-835700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>471600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1926700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2238600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-867000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1465500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>4240400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-245800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>197600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>101500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>4000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>200</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LCID_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LCID_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="92">
   <si>
     <t>LCID</t>
   </si>
@@ -656,247 +656,253 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="10" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>259400</v>
+      </c>
+      <c r="E8" s="3">
         <v>235000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>234500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>200000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>200600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>172700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>157200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>137800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>150900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>149400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>257700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>195500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>97300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>57700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>26400</v>
-      </c>
-      <c r="R8" s="3">
-        <v>200</v>
       </c>
       <c r="S8" s="3">
         <v>200</v>
       </c>
       <c r="T8" s="3">
+        <v>200</v>
+      </c>
+      <c r="U8" s="3">
         <v>300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3600</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y8" s="3">
-        <v>0</v>
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>531800</v>
+      </c>
+      <c r="E9" s="3">
         <v>463600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>443200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>412500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>470400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>404800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>410000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>469700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>555800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>500500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>615300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>492500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>292300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>246000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>151500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3300</v>
       </c>
-      <c r="S9" s="3">
-        <v>0</v>
-      </c>
       <c r="T9" s="3">
+        <v>0</v>
+      </c>
+      <c r="U9" s="3">
         <v>100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2500</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
@@ -909,68 +915,71 @@
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-272400</v>
+      </c>
+      <c r="E10" s="3">
         <v>-228500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-208800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-212500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-269800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-232100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-252900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-331900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-404900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-351100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-357600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-297000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-195000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-188300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-125100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-3100</v>
-      </c>
-      <c r="S10" s="3">
-        <v>200</v>
       </c>
       <c r="T10" s="3">
         <v>200</v>
       </c>
       <c r="U10" s="3">
+        <v>200</v>
+      </c>
+      <c r="V10" s="3">
         <v>1100</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
@@ -983,8 +992,11 @@
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1011,68 +1023,69 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>273800</v>
+      </c>
+      <c r="E12" s="3">
         <v>251200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>280300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>324400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>287200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>284600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>243000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>230800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>233500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>229800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>221300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>213800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>200400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>186100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>163600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>242400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>176800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>167400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>169500</v>
       </c>
-      <c r="V12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1085,8 +1098,11 @@
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1159,59 +1175,62 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-120300</v>
+      </c>
+      <c r="E14" s="3">
         <v>13500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>4900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>8900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>29600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>19900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-6000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>22500</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>2700</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1227,47 +1246,50 @@
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>111100</v>
+      </c>
+      <c r="E15" s="3">
         <v>98000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>90800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>69500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>66200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>68800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>67500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>60800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>55400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>49800</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1307,8 +1329,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1332,73 +1357,74 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1062500</v>
+      </c>
+      <c r="E17" s="3">
         <v>927000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>967400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>970500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>967800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>902700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>894000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>890200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>987000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>899100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1007500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>883000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>656500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>655200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>512100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>500000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>249100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>299100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>203300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>300</v>
       </c>
-      <c r="W17" s="3">
-        <v>0</v>
-      </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
+      <c r="X17" s="3">
+        <v>0</v>
       </c>
       <c r="Y17" s="3" t="s">
         <v>3</v>
@@ -1406,68 +1432,71 @@
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-803000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-691900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-733000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-770500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-767200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-729900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-736900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-752400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-836200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-749700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-749800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-687500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-559200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-597500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-485700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-499800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-248900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-298800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-199700</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1480,8 +1509,11 @@
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1508,68 +1540,69 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-120400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-297500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-293700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>254200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-105500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-26000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-26200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-59600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-41200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>40100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>285000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>158400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>339000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>516700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-559900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-24500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-12700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-449100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-111400</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1582,68 +1615,71 @@
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-571600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-296400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-348400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-955100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-595500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-635000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-643200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-632000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-739600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-740000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-409500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-478400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-177800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-42600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-1009200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-509400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-254800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-743000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-306400</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1656,46 +1692,49 @@
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>23700</v>
+      </c>
+      <c r="E22" s="3">
         <v>11900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>10300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>8500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>6700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>7500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>7800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>3300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>6700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>7100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>8100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>900</v>
-      </c>
-      <c r="O22" s="3">
-        <v>100</v>
       </c>
       <c r="P22" s="3">
         <v>100</v>
@@ -1713,10 +1752,10 @@
         <v>100</v>
       </c>
       <c r="U22" s="3">
-        <v>0</v>
-      </c>
-      <c r="V22" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="V22" s="3">
+        <v>0</v>
       </c>
       <c r="W22" s="3" t="s">
         <v>3</v>
@@ -1730,73 +1769,76 @@
       <c r="Z22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-541800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-367500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-396600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-992000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-643500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-680700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-653800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-630600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-763600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-779400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-472800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-530000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-220400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-81000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1045700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-524400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-261700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-747900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-311200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-200</v>
       </c>
-      <c r="W23" s="3">
-        <v>0</v>
-      </c>
-      <c r="X23" s="3" t="s">
-        <v>3</v>
+      <c r="X23" s="3">
+        <v>0</v>
       </c>
       <c r="Y23" s="3" t="s">
         <v>3</v>
@@ -1804,53 +1846,56 @@
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E24" s="3">
         <v>-1400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>200</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-200</v>
-      </c>
-      <c r="N24" s="3">
-        <v>100</v>
       </c>
       <c r="O24" s="3">
         <v>100</v>
       </c>
       <c r="P24" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q24" s="3">
         <v>300</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
         <v>0</v>
       </c>
@@ -1861,16 +1906,16 @@
         <v>0</v>
       </c>
       <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
         <v>100</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
       <c r="W24" s="3">
         <v>0</v>
       </c>
-      <c r="X24" s="3" t="s">
-        <v>3</v>
+      <c r="X24" s="3">
+        <v>0</v>
       </c>
       <c r="Y24" s="3" t="s">
         <v>3</v>
@@ -1878,8 +1923,11 @@
       <c r="Z24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1952,73 +2000,76 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-539400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-366200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-397200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-992500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-643400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-680900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-653800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-630900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-764200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-779500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-472600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-530100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-220400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-81300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1045700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-524400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-261700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-748000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-311300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-200</v>
       </c>
-      <c r="W26" s="3">
-        <v>0</v>
-      </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
+      <c r="X26" s="3">
+        <v>0</v>
       </c>
       <c r="Y26" s="3" t="s">
         <v>3</v>
@@ -2026,73 +2077,76 @@
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-739300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-731100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-636900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-949600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-790300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-684800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-653800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-630900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-764200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-779500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1726900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-530100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-220400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-81300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1045700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-524400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-261700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-2915300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-297500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-200</v>
       </c>
-      <c r="W27" s="3">
-        <v>0</v>
-      </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
+      <c r="X27" s="3">
+        <v>0</v>
       </c>
       <c r="Y27" s="3" t="s">
         <v>3</v>
@@ -2100,8 +2154,11 @@
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2174,8 +2231,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2248,8 +2308,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2322,8 +2385,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2396,68 +2462,71 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>120400</v>
+      </c>
+      <c r="E32" s="3">
         <v>297500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>293700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-254200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>105500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>26000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>26200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>59600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>41200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-40100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-285000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-158400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-339000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-516700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>559900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>24500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>12700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>449100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>111400</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2470,73 +2539,76 @@
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-539400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-366200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-397200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-992500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-643400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-680900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-653800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-630900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-764200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-779500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1726900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-530100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-220400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-81300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1045700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-524400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-261700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-2915300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-297500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-200</v>
       </c>
-      <c r="W33" s="3">
-        <v>0</v>
-      </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
+      <c r="X33" s="3">
+        <v>0</v>
       </c>
       <c r="Y33" s="3" t="s">
         <v>3</v>
@@ -2544,8 +2616,11 @@
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2618,73 +2693,76 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-539400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-366200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-397200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-992500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-643400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-680900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-653800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-630900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-764200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-779500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1726900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-530100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-220400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-81300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1045700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-524400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-261700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-2915300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-297500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-200</v>
       </c>
-      <c r="W35" s="3">
-        <v>0</v>
-      </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
+      <c r="X35" s="3">
+        <v>0</v>
       </c>
       <c r="Y35" s="3" t="s">
         <v>3</v>
@@ -2692,87 +2770,93 @@
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2799,8 +2883,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2827,129 +2912,133 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1795700</v>
+      </c>
+      <c r="E41" s="3">
         <v>1854900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1606900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1893600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1353600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2169500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1369900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1164400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2775300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>900000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1735800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1264100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3157400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5391800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>6262900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>4796900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>557900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>810000</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V41" s="3">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W41" s="3">
         <v>4200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>200</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1030100</v>
+      </c>
+      <c r="E42" s="3">
         <v>1756000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2424100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1578300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1862800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1824900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2489800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>3258200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2474000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2078400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2177200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2078000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1136600</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>0</v>
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R42" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="S42" s="3">
         <v>500</v>
@@ -2957,8 +3046,8 @@
       <c r="T42" s="3">
         <v>500</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>3</v>
+      <c r="U42" s="3">
+        <v>500</v>
       </c>
       <c r="V42" s="3" t="s">
         <v>3</v>
@@ -2969,71 +3058,74 @@
       <c r="X42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y42" s="3">
-        <v>0</v>
+      <c r="Y42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>148000</v>
+      </c>
+      <c r="E43" s="3">
         <v>114600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>131600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>109600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>113400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>138600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>62900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>33900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>27100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>8400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>19500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>27700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>27900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>600</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3043,71 +3135,74 @@
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y43" s="3">
-        <v>0</v>
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>713300</v>
+      </c>
+      <c r="E44" s="3">
         <v>471400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>407800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>506800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>509900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>565700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>696200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>799000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>849800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1017600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>834400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>685300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>553000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>333900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>127300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>61200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>28200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>6300</v>
       </c>
-      <c r="U44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3117,77 +3212,80 @@
       <c r="X44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y44" s="3">
-        <v>0</v>
+      <c r="Y44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>200700</v>
+      </c>
+      <c r="E45" s="3">
         <v>174800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>250600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>96400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>90200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>63200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>67000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>58100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>55800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>51500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>145100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>126300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>118100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>137800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>113700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>100600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>67900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>51200</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V45" s="3">
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W45" s="3">
         <v>1100</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3197,124 +3295,130 @@
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3951100</v>
+      </c>
+      <c r="E46" s="3">
         <v>4423300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4873900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4247000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4001500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4834000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4757200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5391500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6256900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4119800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4912000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4156400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4966500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5864400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>6507000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>4986800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>682400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>868600</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V46" s="3">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W46" s="3">
         <v>5300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>200</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>807800</v>
+      </c>
+      <c r="E47" s="3">
         <v>947200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1050100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>601200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>739100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>688400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>542600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>479700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>288100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>441700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>530000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>513700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>278100</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3330,12 +3434,12 @@
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V47" s="3">
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W47" s="3">
         <v>2070200</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3345,65 +3449,68 @@
       <c r="Z47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3804100</v>
+      </c>
+      <c r="E48" s="3">
         <v>3553100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3474500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3442700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3278600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3189300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3032400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2894700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2698500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2536100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2381900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2166200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1813600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1494200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1344100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1109700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1014400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>899900</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3413,14 +3520,17 @@
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y48" s="3">
-        <v>0</v>
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3493,8 +3603,11 @@
       <c r="Z49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3567,8 +3680,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3641,82 +3757,88 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>306100</v>
+      </c>
+      <c r="E52" s="3">
         <v>294500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>249400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>198300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>204000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>185400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>180600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>175300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>171600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>163300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>55300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>51500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>71200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>43200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>30600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>42700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>39300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>31300</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V52" s="3">
-        <v>0</v>
+      <c r="V52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W52" s="3">
+        <v>0</v>
+      </c>
+      <c r="X52" s="3">
         <v>200</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3789,82 +3911,88 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8869100</v>
+      </c>
+      <c r="E54" s="3">
         <v>9218000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>9647900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8489200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8223300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8897000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8512700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8941200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>9415100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7260900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7879200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6887800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7129400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7401800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>7881700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6139200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1736100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1799800</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V54" s="3">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W54" s="3">
         <v>2075500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>400</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3891,8 +4019,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3919,73 +4048,74 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>213700</v>
+      </c>
+      <c r="E57" s="3">
         <v>121300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>133800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>139200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>113600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>101500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>108700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>104600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>140100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>145700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>229100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>79800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>129100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>66400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>41300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>8900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>14000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>9200</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V57" s="3">
-        <v>0</v>
+      <c r="V57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W57" s="3">
         <v>0</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>3</v>
+      <c r="X57" s="3">
+        <v>0</v>
       </c>
       <c r="Y57" s="3" t="s">
         <v>3</v>
@@ -3993,287 +4123,299 @@
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>292200</v>
+      </c>
+      <c r="E58" s="3">
         <v>242500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>168800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>88400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>105600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>110300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>109200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>86400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>42700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>35600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>20200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>25500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>7100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>8900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>19500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>27900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>10800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2500</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W58" s="3">
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X58" s="3">
         <v>300</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>610500</v>
+      </c>
+      <c r="E59" s="3">
         <v>556800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>549400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>649400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>527100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>596100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>569400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>639700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>498000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>444800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>688300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>719800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>517900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>436600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>335300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>232600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>175000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>247300</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W59" s="3">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X59" s="3">
         <v>100</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1534000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1331500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1165300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1146100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1010900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1036700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1008400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1037900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>885600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1015000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>937600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>825100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>654100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>511900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>396100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>269400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>199800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>259100</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V60" s="3">
-        <v>0</v>
+      <c r="V60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W60" s="3">
+        <v>0</v>
+      </c>
+      <c r="X60" s="3">
         <v>400</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2448700</v>
+      </c>
+      <c r="E61" s="3">
         <v>2315700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2308100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2315900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2310400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2313100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2318700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2319500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2324100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2311500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2073200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2069900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1994600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1994100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1992900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>4700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>4200</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -4289,71 +4431,74 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>500200</v>
+      </c>
+      <c r="E62" s="3">
         <v>609000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>889200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1171400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>624800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>702700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>226100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>177800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>245600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>302600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>518800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>761500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>770400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1066300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1583400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1019900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>164800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1309500</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V62" s="3">
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W62" s="3">
         <v>72500</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4363,8 +4508,11 @@
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4437,8 +4585,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4511,8 +4662,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4585,82 +4739,88 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4596900</v>
+      </c>
+      <c r="E66" s="3">
         <v>4369500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4475300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4745300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4056100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4160400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3661000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3535200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3455200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3629100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3529500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3656600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3419000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3572400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3972400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1294000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>368500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1572800</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V66" s="3">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W66" s="3">
         <v>72500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>400</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4687,8 +4847,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4761,8 +4922,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4835,29 +4999,32 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>1864600</v>
+      </c>
+      <c r="E70" s="3">
         <v>1664800</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>1299800</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>1060200</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>651300</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>504500</v>
       </c>
-      <c r="I70" s="3">
-        <v>0</v>
-      </c>
       <c r="J70" s="3">
         <v>0</v>
       </c>
@@ -4886,14 +5053,14 @@
         <v>0</v>
       </c>
       <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
         <v>5836800</v>
       </c>
-      <c r="T70" s="3">
+      <c r="U70" s="3">
         <v>4454800</v>
       </c>
-      <c r="U70" s="3">
-        <v>0</v>
-      </c>
       <c r="V70" s="3">
         <v>0</v>
       </c>
@@ -4909,8 +5076,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4983,73 +5153,76 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-13818300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-13278900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-12912700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-12515500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-11523000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-10879600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-10198800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-9545000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-8914100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-8149900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-7370300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-6897700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-6367600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-6147200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-6065900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-5020200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-4495800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-4234100</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V72" s="3">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W72" s="3">
         <v>-200</v>
       </c>
-      <c r="W72" s="3">
-        <v>0</v>
-      </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
+      <c r="X72" s="3">
+        <v>0</v>
       </c>
       <c r="Y72" s="3" t="s">
         <v>3</v>
@@ -5057,8 +5230,11 @@
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5131,8 +5307,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5205,8 +5384,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5279,73 +5461,76 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2407600</v>
+      </c>
+      <c r="E76" s="3">
         <v>3183700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3872800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2683700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3515900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4232200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4851700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5406000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5959800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3631900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4349700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3231200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3710400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3829500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3909400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4845200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-4469200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-4227900</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V76" s="3">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W76" s="3">
         <v>2003000</v>
       </c>
-      <c r="W76" s="3">
-        <v>0</v>
-      </c>
-      <c r="X76" s="3" t="s">
-        <v>3</v>
+      <c r="X76" s="3">
+        <v>0</v>
       </c>
       <c r="Y76" s="3" t="s">
         <v>3</v>
@@ -5353,8 +5538,11 @@
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5427,152 +5615,158 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-539400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-366200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-397200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-992500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-643400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-680900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-653800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-630900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-764200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-779500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1726900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-530100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-220400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-81300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1045700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-524400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-261700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-2915300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-297500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-200</v>
       </c>
-      <c r="W81" s="3">
-        <v>0</v>
-      </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
+      <c r="X81" s="3">
+        <v>0</v>
       </c>
       <c r="Y81" s="3" t="s">
         <v>3</v>
@@ -5580,8 +5774,11 @@
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5608,73 +5805,74 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>66200</v>
+      </c>
+      <c r="E83" s="3">
         <v>68800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>67500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>60800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>55400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>49800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>55200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>50700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>42400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>38200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>55200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>50700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>42400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>38200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>36300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>14900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>6800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>4900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>4800</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X83" s="3">
-        <v>0</v>
+      <c r="X83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y83" s="3">
         <v>0</v>
@@ -5682,8 +5880,11 @@
       <c r="Z83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5756,8 +5957,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5830,8 +6034,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5904,8 +6111,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5978,8 +6188,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6052,73 +6265,76 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-830200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-428600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-533100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-462800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-507000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-516700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-474500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-513600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-700400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-801300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-648500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-569500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-513600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-494600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-312700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-291600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-235100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-218700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-192800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-1400</v>
       </c>
-      <c r="W89" s="3">
-        <v>0</v>
-      </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
+      <c r="X89" s="3">
+        <v>0</v>
       </c>
       <c r="Y89" s="3" t="s">
         <v>3</v>
@@ -6126,8 +6342,11 @@
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6154,73 +6373,74 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-182700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-161200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-291600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-159700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-234300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-198200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-272600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-192500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-203700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-241800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-289900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-290100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-309800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-185100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-121900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-92800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-111800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-94800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-103700</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
+      <c r="X91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y91" s="3">
         <v>0</v>
@@ -6228,8 +6448,11 @@
       <c r="Z91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6302,8 +6525,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6376,68 +6602,71 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>694000</v>
+      </c>
+      <c r="E94" s="3">
         <v>614000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1584400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>283700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-311300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>317500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>652200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1132400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-438000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-28700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-392700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1374900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1729000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-185100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-121400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-92800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-111700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-94800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-103700</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6450,8 +6679,11 @@
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6478,8 +6710,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6510,8 +6743,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -6552,8 +6785,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6626,8 +6862,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6700,8 +6939,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6774,82 +7016,88 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>78900</v>
+      </c>
+      <c r="E100" s="3">
         <v>62700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1831000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>719100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>997200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>28000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>35100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>3013600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-5700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1512800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>17600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>4100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-187300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1899600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>4624700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>101000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>511100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>398000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>2075400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>200</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6880,8 +7128,8 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -6922,78 +7170,84 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-57300</v>
+      </c>
+      <c r="E102" s="3">
         <v>248100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-286600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>540100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-815900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>798000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>205600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1610900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1875300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-835700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>471600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1926700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2238600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-867000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1465500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>4240400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-245800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>197600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>101500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>4000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>200</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LCID_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LCID_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="92">
   <si>
     <t>LCID</t>
   </si>
@@ -656,265 +656,271 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>522700</v>
+      </c>
+      <c r="E8" s="3">
         <v>336600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>259400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>235000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>234500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>200000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>200600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>172700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>157200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>137800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>150900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>149400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>257700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>195500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>97300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>57700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>26400</v>
-      </c>
-      <c r="T8" s="3">
-        <v>200</v>
       </c>
       <c r="U8" s="3">
         <v>200</v>
       </c>
       <c r="V8" s="3">
+        <v>200</v>
+      </c>
+      <c r="W8" s="3">
         <v>300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3600</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA8" s="3">
-        <v>0</v>
+      <c r="AA8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>944600</v>
+      </c>
+      <c r="E9" s="3">
         <v>670200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>531800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>463600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>443200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>412500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>470400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>404800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>410000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>469700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>555800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>500500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>615300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>492500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>292300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>246000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>151500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3300</v>
       </c>
-      <c r="U9" s="3">
-        <v>0</v>
-      </c>
       <c r="V9" s="3">
+        <v>0</v>
+      </c>
+      <c r="W9" s="3">
         <v>100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2500</v>
       </c>
-      <c r="X9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
@@ -927,74 +933,77 @@
       <c r="AB9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-421900</v>
+      </c>
+      <c r="E10" s="3">
         <v>-333600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-272400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-228500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-208800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-212500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-269800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-232100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-252900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-331900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-404900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-351100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-357600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-297000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-195000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-188300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>-125100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>-3100</v>
-      </c>
-      <c r="U10" s="3">
-        <v>200</v>
       </c>
       <c r="V10" s="3">
         <v>200</v>
       </c>
       <c r="W10" s="3">
+        <v>200</v>
+      </c>
+      <c r="X10" s="3">
         <v>1100</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1007,8 +1016,11 @@
       <c r="AB10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1037,74 +1049,75 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>361000</v>
+      </c>
+      <c r="E12" s="3">
         <v>325300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>273800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>251200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>280300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>324400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>287200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>284600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>243000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>230800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>233500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>229800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>221300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>213800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>200400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>186100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>163600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>242400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>176800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>167400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>169500</v>
       </c>
-      <c r="X12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1117,8 +1130,11 @@
       <c r="AB12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1197,65 +1213,68 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E14" s="3">
         <v>-900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-120300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>13500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>4900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>8900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>29600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>19900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-6000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>22500</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>2700</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1271,53 +1290,56 @@
       <c r="Z14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>122100</v>
+      </c>
+      <c r="E15" s="3">
         <v>120100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>111100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>98000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>90800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>69500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>66200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>68800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>67500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>60800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>55400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>49800</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1357,8 +1379,11 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1384,79 +1409,80 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1587500</v>
+      </c>
+      <c r="E17" s="3">
         <v>1278600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1062500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>927000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>967400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>970500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>967800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>902700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>894000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>890200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>987000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>899100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1007500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>883000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>656500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>655200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>512100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>500000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>249100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>299100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>203300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>300</v>
       </c>
-      <c r="Y17" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z17" s="3" t="s">
-        <v>3</v>
+      <c r="Z17" s="3">
+        <v>0</v>
       </c>
       <c r="AA17" s="3" t="s">
         <v>3</v>
@@ -1464,74 +1490,77 @@
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1064800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-942000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-803000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-691900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-733000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-770500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-767200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-729900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-736900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-752400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-836200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-749700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-749800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-687500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-559200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-597500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-485700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-499800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-248900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-298800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-199700</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1544,8 +1573,11 @@
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1574,74 +1606,75 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-262900</v>
+      </c>
+      <c r="E20" s="3">
         <v>46800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-120400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-297500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-293700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>254200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-105500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-26000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-26200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-59600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-41200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>40100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>285000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>158400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>339000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>516700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-559900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-24500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-12700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-449100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-111400</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1654,74 +1687,77 @@
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-679700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-868700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-571600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-296400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-348400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-955100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-595500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-635000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-643200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-632000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-739600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-740000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-409500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-478400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-177800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-42600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-1009200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-509400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-254800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-743000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-306400</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1734,52 +1770,55 @@
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>33900</v>
+      </c>
+      <c r="E22" s="3">
         <v>25600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>23700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>11900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>10300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>8500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>6700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>7500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>7800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>3300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>6700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>7100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>8100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>900</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>100</v>
       </c>
       <c r="R22" s="3">
         <v>100</v>
@@ -1797,10 +1836,10 @@
         <v>100</v>
       </c>
       <c r="W22" s="3">
-        <v>0</v>
-      </c>
-      <c r="X22" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="X22" s="3">
+        <v>0</v>
       </c>
       <c r="Y22" s="3" t="s">
         <v>3</v>
@@ -1814,79 +1853,82 @@
       <c r="AB22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-812300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-978800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-541800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-367500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-396600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-992000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-643500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-680700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-653800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-630600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-763600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-779400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-472800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-530000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-220400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-81000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-1045700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-524400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-261700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-747900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-311200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-200</v>
       </c>
-      <c r="Y23" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z23" s="3" t="s">
-        <v>3</v>
+      <c r="Z23" s="3">
+        <v>0</v>
       </c>
       <c r="AA23" s="3" t="s">
         <v>3</v>
@@ -1894,59 +1936,62 @@
       <c r="AB23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E24" s="3">
         <v>-400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-2400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-1400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>200</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-200</v>
-      </c>
-      <c r="P24" s="3">
-        <v>100</v>
       </c>
       <c r="Q24" s="3">
         <v>100</v>
       </c>
       <c r="R24" s="3">
+        <v>100</v>
+      </c>
+      <c r="S24" s="3">
         <v>300</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
       <c r="T24" s="3">
         <v>0</v>
       </c>
@@ -1957,16 +2002,16 @@
         <v>0</v>
       </c>
       <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
         <v>100</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
-      </c>
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-      <c r="Z24" s="3" t="s">
-        <v>3</v>
+      <c r="Z24" s="3">
+        <v>0</v>
       </c>
       <c r="AA24" s="3" t="s">
         <v>3</v>
@@ -1974,8 +2019,11 @@
       <c r="AB24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2054,79 +2102,82 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-814000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-978400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-539400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-366200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-397200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-992500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-643400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-680900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-653800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-630900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-764200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-779500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-472600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-530100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-220400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-81300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1045700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-524400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-261700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-748000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-311300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-200</v>
       </c>
-      <c r="Y26" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z26" s="3" t="s">
-        <v>3</v>
+      <c r="Z26" s="3">
+        <v>0</v>
       </c>
       <c r="AA26" s="3" t="s">
         <v>3</v>
@@ -2134,79 +2185,82 @@
       <c r="AB26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1176800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1034500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-739300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-731100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-636900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-949600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-790300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-684800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-653800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-630900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-764200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-779500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1726900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-530100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-220400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-81300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1045700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-524400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-261700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-2915300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-297500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-200</v>
       </c>
-      <c r="Y27" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z27" s="3" t="s">
-        <v>3</v>
+      <c r="Z27" s="3">
+        <v>0</v>
       </c>
       <c r="AA27" s="3" t="s">
         <v>3</v>
@@ -2214,8 +2268,11 @@
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2294,8 +2351,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2374,8 +2434,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2454,8 +2517,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2534,74 +2600,77 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>262900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-46800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>120400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>297500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>293700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-254200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>105500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>26000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>26200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>59600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>41200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-40100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-285000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-158400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-339000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-516700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>559900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>24500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>12700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>449100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>111400</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2614,79 +2683,82 @@
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-814000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-978400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-539400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-366200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-397200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-992500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-643400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-680900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-653800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-630900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-764200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-779500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1726900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-530100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-220400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-81300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1045700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-524400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-261700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-2915300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-297500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-200</v>
       </c>
-      <c r="Y33" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z33" s="3" t="s">
-        <v>3</v>
+      <c r="Z33" s="3">
+        <v>0</v>
       </c>
       <c r="AA33" s="3" t="s">
         <v>3</v>
@@ -2694,8 +2766,11 @@
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2774,79 +2849,82 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-814000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-978400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-539400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-366200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-397200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-992500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-643400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-680900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-653800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-630900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-764200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-779500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1726900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-530100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-220400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-81300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1045700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-524400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-261700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-2915300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-297500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-200</v>
       </c>
-      <c r="Y35" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z35" s="3" t="s">
-        <v>3</v>
+      <c r="Z35" s="3">
+        <v>0</v>
       </c>
       <c r="AA35" s="3" t="s">
         <v>3</v>
@@ -2854,93 +2932,99 @@
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2969,8 +3053,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2999,141 +3084,145 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>997800</v>
+      </c>
+      <c r="E41" s="3">
         <v>1635100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1795700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1854900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1606900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1893600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1353600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2169500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1369900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1164400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2775300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>900000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1735800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1264100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3157400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5391800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>6262900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>4796900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>557900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>810000</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X41" s="3">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y41" s="3">
         <v>4200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>200</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>631100</v>
+      </c>
+      <c r="E42" s="3">
         <v>701900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1030100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1756000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2424100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1578300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1862800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1824900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2489800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>3258200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2474000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2078400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>2177200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>2078000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>1136600</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S42" s="3">
-        <v>0</v>
+      <c r="S42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T42" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="U42" s="3">
         <v>500</v>
@@ -3141,8 +3230,8 @@
       <c r="V42" s="3">
         <v>500</v>
       </c>
-      <c r="W42" s="3" t="s">
-        <v>3</v>
+      <c r="W42" s="3">
+        <v>500</v>
       </c>
       <c r="X42" s="3" t="s">
         <v>3</v>
@@ -3153,77 +3242,80 @@
       <c r="Z42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA42" s="3">
-        <v>0</v>
+      <c r="AA42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>190300</v>
+      </c>
+      <c r="E43" s="3">
         <v>155000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>148000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>114600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>131600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>109600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>113400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>138600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>62900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>33900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>27100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>8400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>19500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>27700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>27900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>600</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3233,77 +3325,80 @@
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA43" s="3">
-        <v>0</v>
+      <c r="AA43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1109500</v>
+      </c>
+      <c r="E44" s="3">
         <v>981100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>713300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>471400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>407800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>506800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>509900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>565700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>696200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>799000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>849800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1017600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>834400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>685300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>553000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>333900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>127300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>61200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>28200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>6300</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3313,83 +3408,86 @@
       <c r="Z44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA44" s="3">
-        <v>0</v>
+      <c r="AA44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>291500</v>
+      </c>
+      <c r="E45" s="3">
         <v>264800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>200700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>174800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>250600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>96400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>90200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>63200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>67000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>58100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>55800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>51500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>145100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>126300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>118100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>137800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>113700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>100600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>67900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>51200</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X45" s="3">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y45" s="3">
         <v>1100</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3399,136 +3497,142 @@
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3299700</v>
+      </c>
+      <c r="E46" s="3">
         <v>3800100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3951100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4423300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4873900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4247000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4001500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4834000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4757200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5391500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6256900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4119800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4912000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4156400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>4966500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5864400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>6507000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4986800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>682400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>868600</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X46" s="3">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y46" s="3">
         <v>5300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>200</v>
       </c>
-      <c r="Z46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>512200</v>
+      </c>
+      <c r="E47" s="3">
         <v>687700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>807800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>947200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1050100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>601200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>739100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>688400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>542600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>479700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>288100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>441700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>530000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>513700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>278100</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3544,12 +3648,12 @@
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X47" s="3">
+      <c r="X47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y47" s="3">
         <v>2070200</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3559,71 +3663,74 @@
       <c r="AB47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4220100</v>
+      </c>
+      <c r="E48" s="3">
         <v>3980100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3804100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3553100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3474500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3442700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3278600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3189300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3032400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2894700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2698500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2536100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2381900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2166200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1813600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1494200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1344100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1109700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1014400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>899900</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3633,14 +3740,17 @@
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA48" s="3">
-        <v>0</v>
+      <c r="AA48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3719,8 +3829,11 @@
       <c r="AB49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3799,8 +3912,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3879,88 +3995,94 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>355000</v>
+      </c>
+      <c r="E52" s="3">
         <v>355200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>306100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>294500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>249400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>198300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>204000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>185400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>180600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>175300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>171600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>163300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>55300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>51500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>71200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>43200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>30600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>42700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>39300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>31300</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X52" s="3">
-        <v>0</v>
+      <c r="X52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="3">
         <v>200</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4039,88 +4161,94 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8387000</v>
+      </c>
+      <c r="E54" s="3">
         <v>8823000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8869100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>9218000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>9647900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8489200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8223300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8897000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8512700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8941200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>9415100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7260900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7879200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6887800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>7129400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>7401800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>7881700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6139200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1736100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1799800</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X54" s="3">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y54" s="3">
         <v>2075500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>400</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4149,8 +4277,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4179,79 +4308,80 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>487500</v>
+      </c>
+      <c r="E57" s="3">
         <v>393000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>213700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>121300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>133800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>139200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>113600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>101500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>108700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>104600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>140100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>145700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>229100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>79800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>129100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>66400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>41300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>8900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>14000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>9200</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X57" s="3">
-        <v>0</v>
+      <c r="X57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y57" s="3">
         <v>0</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>3</v>
+      <c r="Z57" s="3">
+        <v>0</v>
       </c>
       <c r="AA57" s="3" t="s">
         <v>3</v>
@@ -4259,311 +4389,323 @@
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>820100</v>
+      </c>
+      <c r="E58" s="3">
         <v>450600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>292200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>242500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>168800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>88400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>105600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>110300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>109200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>86400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>42700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>35600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>20200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>25500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>7100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>8900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>19500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>27900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>10800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2500</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z58" s="3">
         <v>300</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>796400</v>
+      </c>
+      <c r="E59" s="3">
         <v>791200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>610500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>556800</v>
       </c>
-      <c r="G59" s="3">
-        <v>549400</v>
-      </c>
       <c r="H59" s="3">
+        <v>527100</v>
+      </c>
+      <c r="I59" s="3">
         <v>649400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>527100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>596100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>569400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>639700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>498000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>444800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>688300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>719800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>517900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>436600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>335300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>232600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>175000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>247300</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z59" s="3">
         <v>100</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2636100</v>
+      </c>
+      <c r="E60" s="3">
         <v>2105000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1534000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1331500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1165300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1146100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1010900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1036700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1008400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1037900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>885600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1015000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>937600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>825100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>654100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>511900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>396100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>269400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>199800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>259100</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X60" s="3">
-        <v>0</v>
+      <c r="X60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z60" s="3">
         <v>400</v>
       </c>
-      <c r="Z60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2376600</v>
+      </c>
+      <c r="E61" s="3">
         <v>2363000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2448700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2315700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2308100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2315900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2310400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2313100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2318700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2319500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2324100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2311500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2073200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2069900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1994600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1994100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1992900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>4700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>4200</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
@@ -4579,77 +4721,80 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>258700</v>
+      </c>
+      <c r="E62" s="3">
         <v>519200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>500200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>609000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>889200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1171400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>624800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>702700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>226100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>177800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>245600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>302600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>518800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>761500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>770400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1066300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1583400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1019900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>164800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1309500</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X62" s="3">
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y62" s="3">
         <v>72500</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4659,8 +4804,11 @@
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4739,8 +4887,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4819,8 +4970,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4899,88 +5053,94 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5386200</v>
+      </c>
+      <c r="E66" s="3">
         <v>5101900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4596900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4369500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4475300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4745300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4056100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4160400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3661000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3535200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3455200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3629100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3529500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3656600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3419000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3572400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3972400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1294000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>368500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1572800</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X66" s="3">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y66" s="3">
         <v>72500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>400</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5009,8 +5169,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5089,8 +5250,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5169,35 +5333,38 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>2283500</v>
+      </c>
+      <c r="E70" s="3">
         <v>1920700</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>1864600</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>1664800</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>1299800</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>1060200</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>651300</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>504500</v>
       </c>
-      <c r="K70" s="3">
-        <v>0</v>
-      </c>
       <c r="L70" s="3">
         <v>0</v>
       </c>
@@ -5226,14 +5393,14 @@
         <v>0</v>
       </c>
       <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
         <v>5836800</v>
       </c>
-      <c r="V70" s="3">
+      <c r="W70" s="3">
         <v>4454800</v>
       </c>
-      <c r="W70" s="3">
-        <v>0</v>
-      </c>
       <c r="X70" s="3">
         <v>0</v>
       </c>
@@ -5249,8 +5416,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5329,79 +5499,82 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-15610700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-14796700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-13818300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-13278900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-12912700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-12515500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-11523000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-10879600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-10198800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-9545000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-8914100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-8149900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-7370300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-6897700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-6367600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-6147200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-6065900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-5020200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-4495800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-4234100</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X72" s="3">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y72" s="3">
         <v>-200</v>
       </c>
-      <c r="Y72" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z72" s="3" t="s">
-        <v>3</v>
+      <c r="Z72" s="3">
+        <v>0</v>
       </c>
       <c r="AA72" s="3" t="s">
         <v>3</v>
@@ -5409,8 +5582,11 @@
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5489,8 +5665,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5569,8 +5748,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5649,79 +5831,82 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>717300</v>
+      </c>
+      <c r="E76" s="3">
         <v>1800400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2407600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3183700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3872800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2683700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3515900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4232200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4851700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5406000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5959800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3631900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4349700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3231200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3710400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3829500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3909400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4845200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-4469200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-4227900</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X76" s="3">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y76" s="3">
         <v>2003000</v>
       </c>
-      <c r="Y76" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z76" s="3" t="s">
-        <v>3</v>
+      <c r="Z76" s="3">
+        <v>0</v>
       </c>
       <c r="AA76" s="3" t="s">
         <v>3</v>
@@ -5729,8 +5914,11 @@
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5809,164 +5997,170 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-814000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-978400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-539400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-366200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-397200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-992500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-643400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-680900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-653800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-630900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-764200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-779500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1726900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-530100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-220400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-81300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1045700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-524400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-261700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-2915300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-297500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-200</v>
       </c>
-      <c r="Y81" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z81" s="3" t="s">
-        <v>3</v>
+      <c r="Z81" s="3">
+        <v>0</v>
       </c>
       <c r="AA81" s="3" t="s">
         <v>3</v>
@@ -5974,8 +6168,11 @@
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6004,79 +6201,80 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>90800</v>
+      </c>
+      <c r="E83" s="3">
         <v>69500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>66200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>68800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>67500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>60800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>55400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>49800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>55200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>50700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>42400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>38200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>55200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>50700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>42400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>38200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>36300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>14900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>6800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>4900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>4800</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z83" s="3">
-        <v>0</v>
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA83" s="3">
         <v>0</v>
@@ -6084,8 +6282,11 @@
       <c r="AB83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6164,8 +6365,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6244,8 +6448,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6324,8 +6531,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6404,8 +6614,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6484,79 +6697,82 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-916400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-756700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-830200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-428600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-533100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-462800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-507000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-516700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-474500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-513600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-700400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-801300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-648500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-569500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-513600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-494600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-312700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-291600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-235100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-218700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-192800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y89" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z89" s="3" t="s">
-        <v>3</v>
+      <c r="Z89" s="3">
+        <v>0</v>
       </c>
       <c r="AA89" s="3" t="s">
         <v>3</v>
@@ -6564,8 +6780,11 @@
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6594,79 +6813,80 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-325400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-198800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-182700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-161200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-291600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-159700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-234300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-198200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-272600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-192500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-203700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-241800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-289900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-290100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-309800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-185100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-121900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-92800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-111800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-94800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-103700</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z91" s="3">
-        <v>0</v>
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA91" s="3">
         <v>0</v>
@@ -6674,8 +6894,11 @@
       <c r="AB91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6754,8 +6977,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6834,74 +7060,77 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-84700</v>
+      </c>
+      <c r="E94" s="3">
         <v>255100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>694000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>614000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1584400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>283700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-311300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>317500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>652200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1132400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-438000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-28700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-392700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1374900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1729000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-185100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-121400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-92800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-111700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-94800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-103700</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6914,8 +7143,11 @@
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6944,8 +7176,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6982,8 +7215,8 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -7024,8 +7257,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7104,8 +7340,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7184,8 +7423,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7264,88 +7506,94 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>369600</v>
+      </c>
+      <c r="E100" s="3">
         <v>376100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>78900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>62700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1831000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>719100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>997200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>28000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>35100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>3013600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-5700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1512800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>17600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>4100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-187300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1899600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>4624700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>101000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>511100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>398000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>2075400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>200</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7382,8 +7630,8 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -7424,84 +7672,90 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-631500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-125500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-57300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>248100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-286600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>540100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-815900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>798000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>205600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1610900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1875300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-835700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>471600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1926700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2238600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-867000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1465500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>4240400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-245800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>197600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>101500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>4000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>200</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LCID_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LCID_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="92">
   <si>
     <t>LCID</t>
   </si>
@@ -656,274 +656,280 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AC7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>282500</v>
+      </c>
+      <c r="E8" s="3">
         <v>522700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>336600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>259400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>235000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>234500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>200000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>200600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>172700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>157200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>137800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>150900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>149400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>257700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>195500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>97300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>57700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>26400</v>
-      </c>
-      <c r="U8" s="3">
-        <v>200</v>
       </c>
       <c r="V8" s="3">
         <v>200</v>
       </c>
       <c r="W8" s="3">
+        <v>200</v>
+      </c>
+      <c r="X8" s="3">
         <v>300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3600</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB8" s="3">
-        <v>0</v>
+      <c r="AB8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>594200</v>
+      </c>
+      <c r="E9" s="3">
         <v>944600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>670200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>531800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>463600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>443200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>412500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>470400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>404800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>410000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>469700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>555800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>500500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>615300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>492500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>292300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>246000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>151500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3300</v>
       </c>
-      <c r="V9" s="3">
-        <v>0</v>
-      </c>
       <c r="W9" s="3">
+        <v>0</v>
+      </c>
+      <c r="X9" s="3">
         <v>100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2500</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
@@ -936,77 +942,80 @@
       <c r="AC9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-311700</v>
+      </c>
+      <c r="E10" s="3">
         <v>-421900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-333600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-272400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-228500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-208800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-212500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-269800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-232100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-252900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-331900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-404900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-351100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-357600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-297000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-195000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>-188300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>-125100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>-3100</v>
-      </c>
-      <c r="V10" s="3">
-        <v>200</v>
       </c>
       <c r="W10" s="3">
         <v>200</v>
       </c>
       <c r="X10" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y10" s="3">
         <v>1100</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1019,8 +1028,11 @@
       <c r="AC10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1050,77 +1062,78 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>335700</v>
+      </c>
+      <c r="E12" s="3">
         <v>361000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>325300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>273800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>251200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>280300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>324400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>287200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>284600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>243000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>230800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>233500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>229800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>221300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>213800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>200400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>186100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>163600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>242400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>176800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>167400</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>169500</v>
       </c>
-      <c r="Y12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1133,8 +1146,11 @@
       <c r="AC12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1216,68 +1232,71 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>48200</v>
+      </c>
+      <c r="E14" s="3">
         <v>1800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-120300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>13500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>4900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>8900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>29600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>19900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-6000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>22500</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>2700</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1293,56 +1312,59 @@
       <c r="AA14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>116400</v>
+      </c>
+      <c r="E15" s="3">
         <v>122100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>120100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>111100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>98000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>90800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>69500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>66200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>68800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>67500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>60800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>55400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>49800</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1382,8 +1404,11 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1410,82 +1435,83 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1234000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1587500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1278600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1062500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>927000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>967400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>970500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>967800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>902700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>894000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>890200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>987000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>899100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1007500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>883000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>656500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>655200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>512100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>500000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>249100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>299100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>203300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>300</v>
       </c>
-      <c r="Z17" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA17" s="3" t="s">
-        <v>3</v>
+      <c r="AA17" s="3">
+        <v>0</v>
       </c>
       <c r="AB17" s="3" t="s">
         <v>3</v>
@@ -1493,77 +1519,80 @@
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-951600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1064800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-942000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-803000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-691900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-733000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-770500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-767200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-729900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-736900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-752400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-836200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-749700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-749800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-687500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-559200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-597500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-485700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-499800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-248900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-298800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-199700</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1576,8 +1605,11 @@
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1607,77 +1639,78 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-262900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>46800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-120400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-297500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-293700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>254200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-105500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-26000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-26200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-59600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-41200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>40100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>285000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>158400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>339000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>516700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-559900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-24500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-12700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-449100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-111400</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1690,77 +1723,80 @@
       <c r="AC20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-835600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-679700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-868700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-571600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-296400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-348400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-955100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-595500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-635000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-643200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-632000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-739600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-740000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-409500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-478400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-177800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-42600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-1009200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-509400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-254800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-743000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-306400</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1773,55 +1809,58 @@
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>41100</v>
+      </c>
+      <c r="E22" s="3">
         <v>33900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>25600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>23700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>11900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>10300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>8500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>6700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>7500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>7800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>3300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>6700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>7100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>8100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>900</v>
-      </c>
-      <c r="R22" s="3">
-        <v>100</v>
       </c>
       <c r="S22" s="3">
         <v>100</v>
@@ -1839,10 +1878,10 @@
         <v>100</v>
       </c>
       <c r="X22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>0</v>
       </c>
       <c r="Z22" s="3" t="s">
         <v>3</v>
@@ -1856,82 +1895,85 @@
       <c r="AC22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1028200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-812300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-978800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-541800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-367500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-396600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-992000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-643500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-680700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-653800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-630600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-763600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-779400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-472800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-530000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-220400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-81000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1045700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-524400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-261700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-747900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-311200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-200</v>
       </c>
-      <c r="Z23" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA23" s="3" t="s">
-        <v>3</v>
+      <c r="AA23" s="3">
+        <v>0</v>
       </c>
       <c r="AB23" s="3" t="s">
         <v>3</v>
@@ -1939,62 +1981,65 @@
       <c r="AC23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>200</v>
+      </c>
+      <c r="E24" s="3">
         <v>1800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-2400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-1400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>200</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-200</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>100</v>
       </c>
       <c r="R24" s="3">
         <v>100</v>
       </c>
       <c r="S24" s="3">
+        <v>100</v>
+      </c>
+      <c r="T24" s="3">
         <v>300</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
       <c r="U24" s="3">
         <v>0</v>
       </c>
@@ -2005,16 +2050,16 @@
         <v>0</v>
       </c>
       <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
         <v>100</v>
       </c>
-      <c r="Y24" s="3">
-        <v>0</v>
-      </c>
       <c r="Z24" s="3">
         <v>0</v>
       </c>
-      <c r="AA24" s="3" t="s">
-        <v>3</v>
+      <c r="AA24" s="3">
+        <v>0</v>
       </c>
       <c r="AB24" s="3" t="s">
         <v>3</v>
@@ -2022,8 +2067,11 @@
       <c r="AC24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2105,82 +2153,85 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1028300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-814000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-978400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-539400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-366200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-397200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-992500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-643400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-680900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-653800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-630900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-764200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-779500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-472600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-530100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-220400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-81300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1045700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-524400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-261700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-748000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-311300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-200</v>
       </c>
-      <c r="Z26" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA26" s="3" t="s">
-        <v>3</v>
+      <c r="AA26" s="3">
+        <v>0</v>
       </c>
       <c r="AB26" s="3" t="s">
         <v>3</v>
@@ -2188,82 +2239,85 @@
       <c r="AC26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1134300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1176800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1034500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-739300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-731100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-636900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-949600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-790300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-684800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-653800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-630900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-764200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-779500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1726900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-530100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-220400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-81300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1045700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-524400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-261700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-2915300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-297500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-200</v>
       </c>
-      <c r="Z27" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA27" s="3" t="s">
-        <v>3</v>
+      <c r="AA27" s="3">
+        <v>0</v>
       </c>
       <c r="AB27" s="3" t="s">
         <v>3</v>
@@ -2271,8 +2325,11 @@
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2354,8 +2411,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2437,8 +2497,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2520,8 +2583,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2603,77 +2669,80 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E32" s="3">
         <v>262900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-46800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>120400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>297500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>293700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-254200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>105500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>26000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>26200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>59600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>41200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-40100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-285000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-158400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-339000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-516700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>559900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>24500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>12700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>449100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>111400</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2686,82 +2755,85 @@
       <c r="AC32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1028300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-814000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-978400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-539400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-366200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-397200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-992500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-643400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-680900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-653800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-630900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-764200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-779500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1726900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-530100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-220400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-81300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1045700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-524400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-261700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-2915300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-297500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-200</v>
       </c>
-      <c r="Z33" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA33" s="3" t="s">
-        <v>3</v>
+      <c r="AA33" s="3">
+        <v>0</v>
       </c>
       <c r="AB33" s="3" t="s">
         <v>3</v>
@@ -2769,8 +2841,11 @@
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2852,82 +2927,85 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1028300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-814000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-978400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-539400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-366200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-397200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-992500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-643400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-680900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-653800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-630900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-764200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-779500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1726900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-530100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-220400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-81300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1045700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-524400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-261700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-2915300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-297500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-200</v>
       </c>
-      <c r="Z35" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA35" s="3" t="s">
-        <v>3</v>
+      <c r="AA35" s="3">
+        <v>0</v>
       </c>
       <c r="AB35" s="3" t="s">
         <v>3</v>
@@ -2935,96 +3013,102 @@
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AC38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3054,8 +3138,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3085,147 +3170,151 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>700400</v>
+      </c>
+      <c r="E41" s="3">
         <v>997800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1635100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1795700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1854900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1606900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1893600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1353600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2169500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1369900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1164400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2775300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>900000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1735800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1264100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3157400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5391800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6262900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>4796900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>557900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>810000</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y41" s="3">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z41" s="3">
         <v>4200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>200</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>631100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>701900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1030100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1756000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2424100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1578300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1862800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1824900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2489800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>3258200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2474000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>2078400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>2177200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>2078000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>1136600</v>
       </c>
-      <c r="S42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T42" s="3">
-        <v>0</v>
+      <c r="T42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U42" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="V42" s="3">
         <v>500</v>
@@ -3233,8 +3322,8 @@
       <c r="W42" s="3">
         <v>500</v>
       </c>
-      <c r="X42" s="3" t="s">
-        <v>3</v>
+      <c r="X42" s="3">
+        <v>500</v>
       </c>
       <c r="Y42" s="3" t="s">
         <v>3</v>
@@ -3245,80 +3334,83 @@
       <c r="AA42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB42" s="3">
-        <v>0</v>
+      <c r="AB42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>131200</v>
+      </c>
+      <c r="E43" s="3">
         <v>190300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>155000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>148000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>114600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>131600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>109600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>113400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>138600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>62900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>33900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>27100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>8400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>19500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>27700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>27900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>600</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3328,80 +3420,83 @@
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB43" s="3">
-        <v>0</v>
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1468900</v>
+      </c>
+      <c r="E44" s="3">
         <v>1109500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>981100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>713300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>471400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>407800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>506800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>509900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>565700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>696200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>799000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>849800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1017600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>834400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>685300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>553000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>333900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>127300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>61200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>28200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>6300</v>
       </c>
-      <c r="X44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3411,86 +3506,89 @@
       <c r="AA44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB44" s="3">
-        <v>0</v>
+      <c r="AB44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>353800</v>
+      </c>
+      <c r="E45" s="3">
         <v>291500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>264800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>200700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>174800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>250600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>96400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>90200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>63200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>67000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>58100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>55800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>51500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>145100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>126300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>118100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>137800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>113700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>100600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>67900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>51200</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y45" s="3">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z45" s="3">
         <v>1100</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3500,142 +3598,148 @@
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2756700</v>
+      </c>
+      <c r="E46" s="3">
         <v>3299700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3800100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3951100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4423300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4873900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4247000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4001500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4834000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4757200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5391500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>6256900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4119800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4912000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>4156400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>4966500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>5864400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>6507000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4986800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>682400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>868600</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y46" s="3">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z46" s="3">
         <v>5300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>200</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>13600</v>
+      </c>
+      <c r="E47" s="3">
         <v>512200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>687700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>807800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>947200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1050100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>601200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>739100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>688400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>542600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>479700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>288100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>441700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>530000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>513700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>278100</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3651,12 +3755,12 @@
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Y47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z47" s="3">
         <v>2070200</v>
       </c>
-      <c r="Z47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3666,74 +3770,77 @@
       <c r="AC47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4287200</v>
+      </c>
+      <c r="E48" s="3">
         <v>4220100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3980100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3804100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3553100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3474500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3442700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3278600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3189300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3032400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2894700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2698500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2536100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2381900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2166200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1813600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1494200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1344100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1109700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1014400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>899900</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3743,14 +3850,17 @@
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB48" s="3">
-        <v>0</v>
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3832,8 +3942,11 @@
       <c r="AC49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3915,8 +4028,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3998,91 +4114,97 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>425700</v>
+      </c>
+      <c r="E52" s="3">
         <v>355000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>355200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>306100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>294500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>249400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>198300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>204000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>185400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>180600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>175300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>171600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>163300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>55300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>51500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>71200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>43200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>30600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>42700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>39300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>31300</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y52" s="3">
-        <v>0</v>
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="3">
         <v>200</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4164,91 +4286,97 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7483200</v>
+      </c>
+      <c r="E54" s="3">
         <v>8387000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8823000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8869100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>9218000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>9647900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8489200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8223300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8897000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8512700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8941200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>9415100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7260900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7879200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6887800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>7129400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>7401800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>7881700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>6139200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1736100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1799800</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y54" s="3">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z54" s="3">
         <v>2075500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>400</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4278,8 +4406,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4309,82 +4438,83 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>484900</v>
+      </c>
+      <c r="E57" s="3">
         <v>487500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>393000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>213700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>121300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>133800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>139200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>113600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>101500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>108700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>104600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>140100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>145700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>229100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>79800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>129100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>66400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>41300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>8900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>14000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>9200</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y57" s="3">
-        <v>0</v>
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z57" s="3">
         <v>0</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>3</v>
+      <c r="AA57" s="3">
+        <v>0</v>
       </c>
       <c r="AB57" s="3" t="s">
         <v>3</v>
@@ -4392,323 +4522,335 @@
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>782300</v>
+      </c>
+      <c r="E58" s="3">
         <v>820100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>450600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>292200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>242500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>168800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>88400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>105600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>110300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>109200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>86400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>42700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>35600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>20200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>25500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>7100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>8900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>19500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>27900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>10800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2500</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA58" s="3">
         <v>300</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>818700</v>
+      </c>
+      <c r="E59" s="3">
         <v>796400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>791200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>610500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>556800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>527100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>649400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>527100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>596100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>569400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>639700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>498000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>444800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>688300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>719800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>517900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>436600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>335300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>232600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>175000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>247300</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA59" s="3">
         <v>100</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2694300</v>
+      </c>
+      <c r="E60" s="3">
         <v>2636100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2105000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1534000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1331500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1165300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1146100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1010900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1036700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1008400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1037900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>885600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1015000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>937600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>825100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>654100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>511900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>396100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>269400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>199800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>259100</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y60" s="3">
-        <v>0</v>
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA60" s="3">
         <v>400</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2385800</v>
+      </c>
+      <c r="E61" s="3">
         <v>2376600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2363000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2448700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2315700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2308100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2315900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2310400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2313100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2318700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2319500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2324100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2311500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2073200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2069900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1994600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1994100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1992900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>4000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>4200</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -4724,80 +4866,83 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>250200</v>
+      </c>
+      <c r="E62" s="3">
         <v>258700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>519200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>500200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>609000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>889200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1171400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>624800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>702700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>226100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>177800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>245600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>302600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>518800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>761500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>770400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1066300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1583400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1019900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>164800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1309500</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y62" s="3">
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z62" s="3">
         <v>72500</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4807,8 +4952,11 @@
       <c r="AC62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4890,8 +5038,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4973,8 +5124,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5056,91 +5210,97 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5445100</v>
+      </c>
+      <c r="E66" s="3">
         <v>5386200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5101900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4596900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4369500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4475300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4745300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4056100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4160400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3661000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3535200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3455200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3629100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3529500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3656600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3419000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3572400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3972400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1294000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>368500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1572800</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y66" s="3">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z66" s="3">
         <v>72500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>400</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5170,8 +5330,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5253,8 +5414,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5336,38 +5500,41 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>2389500</v>
+      </c>
+      <c r="E70" s="3">
         <v>2283500</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>1920700</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>1864600</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>1664800</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>1299800</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>1060200</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>651300</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>504500</v>
       </c>
-      <c r="L70" s="3">
-        <v>0</v>
-      </c>
       <c r="M70" s="3">
         <v>0</v>
       </c>
@@ -5396,14 +5563,14 @@
         <v>0</v>
       </c>
       <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3">
         <v>5836800</v>
       </c>
-      <c r="W70" s="3">
+      <c r="X70" s="3">
         <v>4454800</v>
       </c>
-      <c r="X70" s="3">
-        <v>0</v>
-      </c>
       <c r="Y70" s="3">
         <v>0</v>
       </c>
@@ -5419,8 +5586,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5502,82 +5672,85 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-16639100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-15610700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-14796700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-13818300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-13278900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-12912700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-12515500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-11523000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-10879600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-10198800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-9545000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-8914100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-8149900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-7370300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-6897700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-6367600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-6147200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-6065900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-5020200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-4495800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-4234100</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y72" s="3">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z72" s="3">
         <v>-200</v>
       </c>
-      <c r="Z72" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA72" s="3" t="s">
-        <v>3</v>
+      <c r="AA72" s="3">
+        <v>0</v>
       </c>
       <c r="AB72" s="3" t="s">
         <v>3</v>
@@ -5585,8 +5758,11 @@
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5668,8 +5844,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5751,8 +5930,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5834,82 +6016,85 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-351400</v>
+      </c>
+      <c r="E76" s="3">
         <v>717300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1800400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2407600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3183700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3872800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2683700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3515900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4232200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4851700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5406000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5959800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3631900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4349700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3231200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3710400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3829500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3909400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4845200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-4469200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-4227900</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y76" s="3">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z76" s="3">
         <v>2003000</v>
       </c>
-      <c r="Z76" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA76" s="3" t="s">
-        <v>3</v>
+      <c r="AA76" s="3">
+        <v>0</v>
       </c>
       <c r="AB76" s="3" t="s">
         <v>3</v>
@@ -5917,8 +6102,11 @@
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6000,170 +6188,176 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AC80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1028300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-814000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-978400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-539400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-366200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-397200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-992500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-643400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-680900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-653800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-630900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-764200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-779500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1726900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-530100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-220400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-81300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1045700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-524400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-261700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-2915300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-297500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-200</v>
       </c>
-      <c r="Z81" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA81" s="3" t="s">
-        <v>3</v>
+      <c r="AA81" s="3">
+        <v>0</v>
       </c>
       <c r="AB81" s="3" t="s">
         <v>3</v>
@@ -6171,8 +6365,11 @@
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6202,82 +6399,83 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>98000</v>
+      </c>
+      <c r="E83" s="3">
         <v>90800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>69500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>66200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>68800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>67500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>60800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>55400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>49800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>55200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>50700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>42400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>38200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>55200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>50700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>42400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>38200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>36300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>14900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>6800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>4900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>4800</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA83" s="3">
-        <v>0</v>
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB83" s="3">
         <v>0</v>
@@ -6285,8 +6483,11 @@
       <c r="AC83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6368,8 +6569,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6451,8 +6655,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6534,8 +6741,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6617,8 +6827,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6700,82 +6913,85 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1185700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-916400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-756700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-830200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-428600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-533100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-462800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-507000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-516700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-474500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-513600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-700400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-801300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-648500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-569500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-513600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-494600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-312700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-291600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-235100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-218700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-192800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA89" s="3" t="s">
-        <v>3</v>
+      <c r="AA89" s="3">
+        <v>0</v>
       </c>
       <c r="AB89" s="3" t="s">
         <v>3</v>
@@ -6783,8 +6999,11 @@
       <c r="AC89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6814,82 +7033,83 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-253200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-325400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-198800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-182700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-161200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-291600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-159700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-234300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-198200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-272600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-192500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-203700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-241800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-289900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-290100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-309800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-185100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-121900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-92800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-111800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-94800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-103700</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA91" s="3">
-        <v>0</v>
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB91" s="3">
         <v>0</v>
@@ -6897,8 +7117,11 @@
       <c r="AC91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6980,8 +7203,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7063,77 +7289,80 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>875200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-84700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>255100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>694000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>614000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1584400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>283700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-311300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>317500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>652200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1132400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-438000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-28700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-392700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1374900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1729000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-185100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-121400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-92800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-111700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-94800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-103700</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
@@ -7146,8 +7375,11 @@
       <c r="AC94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7177,8 +7409,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7218,8 +7451,8 @@
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -7260,8 +7493,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7343,8 +7579,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7426,8 +7665,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7509,91 +7751,97 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>35300</v>
+      </c>
+      <c r="E100" s="3">
         <v>369600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>376100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>78900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>62700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1831000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>719100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>997200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>28000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>35100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>3013600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-5700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1512800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>17600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>4100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-187300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1899600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>4624700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>101000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>511100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>398000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>2075400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>200</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7633,8 +7881,8 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -7675,87 +7923,93 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-275200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-631500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-125500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-57300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>248100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-286600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>540100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-815900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>798000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>205600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1610900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1875300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-835700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>471600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1926700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-2238600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-867000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1465500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>4240400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-245800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>197600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>101500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>4000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>200</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
